--- a/管理スプレッドシート.xlsx
+++ b/管理スプレッドシート.xlsx
@@ -4046,23 +4046,57 @@
       <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="7" t="n"/>
+      <c r="A25" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル 財布</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>45241</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>6300</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>45293</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>9700</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>45573</v>
+      </c>
       <c r="L25" s="9">
         <f>IF(K25="","",K25-H25)</f>
         <v/>
       </c>
-      <c r="M25" s="8" t="n"/>
-      <c r="N25" s="8" t="n"/>
+      <c r="M25" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O25" s="8">
         <f>IF(J25="","",J25-G25-M25-N25)</f>
         <v/>
@@ -4071,26 +4105,60 @@
         <f>IF(J25="","",O25/J25)</f>
         <v/>
       </c>
-      <c r="Q25" s="6" t="n"/>
+      <c r="Q25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="3" t="n"/>
+      <c r="A26" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル 財布</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>45241</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>45295</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>13200</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>45607</v>
+      </c>
       <c r="L26" s="5">
         <f>IF(K26="","",K26-H26)</f>
         <v/>
       </c>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
+      <c r="M26" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O26" s="4">
         <f>IF(J26="","",J26-G26-M26-N26)</f>
         <v/>
@@ -4099,26 +4167,60 @@
         <f>IF(J26="","",O26/J26)</f>
         <v/>
       </c>
-      <c r="Q26" s="2" t="n"/>
+      <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="7" t="n"/>
+      <c r="A27" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル 長財布</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>45241</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>6673</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>45295</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>13175</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>45480</v>
+      </c>
       <c r="L27" s="9">
         <f>IF(K27="","",K27-H27)</f>
         <v/>
       </c>
-      <c r="M27" s="8" t="n"/>
-      <c r="N27" s="8" t="n"/>
+      <c r="M27" s="8" t="n">
+        <v>1317</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O27" s="8">
         <f>IF(J27="","",J27-G27-M27-N27)</f>
         <v/>
@@ -4127,26 +4229,60 @@
         <f>IF(J27="","",O27/J27)</f>
         <v/>
       </c>
-      <c r="Q27" s="6" t="n"/>
+      <c r="Q27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="3" t="n"/>
+      <c r="A28" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL 折り財布 レザー キャビアスキン ココマーク ブラック</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>45299</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>45329</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>PayPay</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>14500</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>45481</v>
+      </c>
       <c r="L28" s="5">
         <f>IF(K28="","",K28-H28)</f>
         <v/>
       </c>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
+      <c r="M28" s="4" t="n">
+        <v>723</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O28" s="4">
         <f>IF(J28="","",J28-G28-M28-N28)</f>
         <v/>
@@ -4155,26 +4291,60 @@
         <f>IF(J28="","",O28/J28)</f>
         <v/>
       </c>
-      <c r="Q28" s="2" t="n"/>
+      <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="7" t="n"/>
+      <c r="A29" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL 財布カメリア</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>45334</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>14300</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>45348</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>25400</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>45485</v>
+      </c>
       <c r="L29" s="9">
         <f>IF(K29="","",K29-H29)</f>
         <v/>
       </c>
-      <c r="M29" s="8" t="n"/>
-      <c r="N29" s="8" t="n"/>
+      <c r="M29" s="8" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N29" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O29" s="8">
         <f>IF(J29="","",J29-G29-M29-N29)</f>
         <v/>
@@ -4183,26 +4353,60 @@
         <f>IF(J29="","",O29/J29)</f>
         <v/>
       </c>
-      <c r="Q29" s="6" t="n"/>
+      <c r="Q29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="3" t="n"/>
+      <c r="A30" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン ココマーク ラウンドファスナー長財布</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>45373</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>38500</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>45378</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>51000</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>45551</v>
+      </c>
       <c r="L30" s="5">
         <f>IF(K30="","",K30-H30)</f>
         <v/>
       </c>
-      <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="M30" s="4" t="n">
+        <v>5100</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O30" s="4">
         <f>IF(J30="","",J30-G30-M30-N30)</f>
         <v/>
@@ -4211,26 +4415,60 @@
         <f>IF(J30="","",O30/J30)</f>
         <v/>
       </c>
-      <c r="Q30" s="2" t="n"/>
+      <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="7" t="n"/>
+      <c r="A31" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル 長財布</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>45373</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>34100</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>45378</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>ラクマ</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>45615</v>
+      </c>
       <c r="L31" s="9">
         <f>IF(K31="","",K31-H31)</f>
         <v/>
       </c>
-      <c r="M31" s="8" t="n"/>
-      <c r="N31" s="8" t="n"/>
+      <c r="M31" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>200</v>
+      </c>
       <c r="O31" s="8">
         <f>IF(J31="","",J31-G31-M31-N31)</f>
         <v/>
@@ -4239,26 +4477,60 @@
         <f>IF(J31="","",O31/J31)</f>
         <v/>
       </c>
-      <c r="Q31" s="6" t="n"/>
+      <c r="Q31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="3" t="n"/>
+      <c r="A32" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL(シャネル) Wホック財布 - 黒 キャビアスキン</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>45531</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>7300</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>45534</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>PayPay</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>13600</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>45588</v>
+      </c>
       <c r="L32" s="5">
         <f>IF(K32="","",K32-H32)</f>
         <v/>
       </c>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="M32" s="4" t="n">
+        <v>678</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>200</v>
+      </c>
       <c r="O32" s="4">
         <f>IF(J32="","",J32-G32-M32-N32)</f>
         <v/>
@@ -4267,26 +4539,60 @@
         <f>IF(J32="","",O32/J32)</f>
         <v/>
       </c>
-      <c r="Q32" s="2" t="n"/>
+      <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="7" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="7" t="n"/>
+      <c r="A33" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL(シャネル) 長財布 - 黒 キャビアスキン</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>45531</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>7300</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>45534</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>16700</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>45600</v>
+      </c>
       <c r="L33" s="9">
         <f>IF(K33="","",K33-H33)</f>
         <v/>
       </c>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
+      <c r="M33" s="8" t="n">
+        <v>1670</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O33" s="8">
         <f>IF(J33="","",J33-G33-M33-N33)</f>
         <v/>
@@ -4295,26 +4601,60 @@
         <f>IF(J33="","",O33/J33)</f>
         <v/>
       </c>
-      <c r="Q33" s="6" t="n"/>
+      <c r="Q33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="3" t="n"/>
+      <c r="A34" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL  シャネル ココマーク キャビアスキン 二つ折り財布 財布</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>45532</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>45541</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>45571</v>
+      </c>
       <c r="L34" s="5">
         <f>IF(K34="","",K34-H34)</f>
         <v/>
       </c>
-      <c r="M34" s="4" t="n"/>
-      <c r="N34" s="4" t="n"/>
+      <c r="M34" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O34" s="4">
         <f>IF(J34="","",J34-G34-M34-N34)</f>
         <v/>
@@ -4323,26 +4663,60 @@
         <f>IF(J34="","",O34/J34)</f>
         <v/>
       </c>
-      <c r="Q34" s="2" t="n"/>
+      <c r="Q34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="7" t="n"/>
+      <c r="A35" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL ラムスキン カメリア 折り財布</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>45541</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>45548</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>18200</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>45672</v>
+      </c>
       <c r="L35" s="9">
         <f>IF(K35="","",K35-H35)</f>
         <v/>
       </c>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="8" t="n"/>
+      <c r="M35" s="8" t="n">
+        <v>1820</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O35" s="8">
         <f>IF(J35="","",J35-G35-M35-N35)</f>
         <v/>
@@ -4351,26 +4725,60 @@
         <f>IF(J35="","",O35/J35)</f>
         <v/>
       </c>
-      <c r="Q35" s="6" t="n"/>
+      <c r="Q35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="3" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="3" t="n"/>
+      <c r="A36" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>バッグ</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL チョコバー ゴールド チェーンショルダー</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>45541</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>145200</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>45548</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>170000</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>45718</v>
+      </c>
       <c r="L36" s="5">
         <f>IF(K36="","",K36-H36)</f>
         <v/>
       </c>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
+      <c r="M36" s="4" t="n">
+        <v>16998</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>850</v>
+      </c>
       <c r="O36" s="4">
         <f>IF(J36="","",J36-G36-M36-N36)</f>
         <v/>
@@ -4379,26 +4787,60 @@
         <f>IF(J36="","",O36/J36)</f>
         <v/>
       </c>
-      <c r="Q36" s="2" t="n"/>
+      <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="7" t="n"/>
+      <c r="A37" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル キャビアスキン 二つ折り長財布</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>45574</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>45579</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>17500</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>45636</v>
+      </c>
       <c r="L37" s="9">
         <f>IF(K37="","",K37-H37)</f>
         <v/>
       </c>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
+      <c r="M37" s="8" t="n">
+        <v>1750</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O37" s="8">
         <f>IF(J37="","",J37-G37-M37-N37)</f>
         <v/>
@@ -4407,26 +4849,60 @@
         <f>IF(J37="","",O37/J37)</f>
         <v/>
       </c>
-      <c r="Q37" s="6" t="n"/>
+      <c r="Q37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="3" t="n"/>
+      <c r="A38" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL コインケース</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>45574</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>39600</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>45579</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>45589</v>
+      </c>
       <c r="L38" s="5">
         <f>IF(K38="","",K38-H38)</f>
         <v/>
       </c>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="M38" s="4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O38" s="4">
         <f>IF(J38="","",J38-G38-M38-N38)</f>
         <v/>
@@ -4435,26 +4911,60 @@
         <f>IF(J38="","",O38/J38)</f>
         <v/>
       </c>
-      <c r="Q38" s="2" t="n"/>
+      <c r="Q38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="7" t="n"/>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="7" t="n"/>
+      <c r="A39" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン ココマーク 二つ折りコンパクト財布 黒 ギャランティカード 4662401 財布</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>45611</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>9350</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>45624</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>17700</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>45650</v>
+      </c>
       <c r="L39" s="9">
         <f>IF(K39="","",K39-H39)</f>
         <v/>
       </c>
-      <c r="M39" s="8" t="n"/>
-      <c r="N39" s="8" t="n"/>
+      <c r="M39" s="8" t="n">
+        <v>1770</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O39" s="8">
         <f>IF(J39="","",J39-G39-M39-N39)</f>
         <v/>
@@ -4463,26 +4973,60 @@
         <f>IF(J39="","",O39/J39)</f>
         <v/>
       </c>
-      <c r="Q39" s="6" t="n"/>
+      <c r="Q39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="3" t="n"/>
+      <c r="A40" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン ココマーク 二つ折りがま口財布 黒 6623629 財布</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>45618</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>9350</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>45629</v>
+      </c>
       <c r="L40" s="5">
         <f>IF(K40="","",K40-H40)</f>
         <v/>
       </c>
-      <c r="M40" s="4" t="n"/>
-      <c r="N40" s="4" t="n"/>
+      <c r="M40" s="4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O40" s="4">
         <f>IF(J40="","",J40-G40-M40-N40)</f>
         <v/>
@@ -4491,26 +5035,60 @@
         <f>IF(J40="","",O40/J40)</f>
         <v/>
       </c>
-      <c r="Q40" s="2" t="n"/>
+      <c r="Q40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="7" t="n"/>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="7" t="n"/>
+      <c r="A41" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL GDココ ビコローレ がま口 長財布 財布</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>45628</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>10450</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>45640</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>ラクマ</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="n">
+        <v>16900</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>45717</v>
+      </c>
       <c r="L41" s="9">
         <f>IF(K41="","",K41-H41)</f>
         <v/>
       </c>
-      <c r="M41" s="8" t="n"/>
-      <c r="N41" s="8" t="n"/>
+      <c r="M41" s="8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>200</v>
+      </c>
       <c r="O41" s="8">
         <f>IF(J41="","",J41-G41-M41-N41)</f>
         <v/>
@@ -4519,26 +5097,60 @@
         <f>IF(J41="","",O41/J41)</f>
         <v/>
       </c>
-      <c r="Q41" s="6" t="n"/>
+      <c r="Q41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="3" t="n"/>
+      <c r="A42" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン ココマーク 二つ折りコンパクト財布 黒 シリアルシール半分 財布</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>45633</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>45641</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>18300</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>45661</v>
+      </c>
       <c r="L42" s="5">
         <f>IF(K42="","",K42-H42)</f>
         <v/>
       </c>
-      <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="M42" s="4" t="n">
+        <v>1830</v>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O42" s="4">
         <f>IF(J42="","",J42-G42-M42-N42)</f>
         <v/>
@@ -4547,26 +5159,60 @@
         <f>IF(J42="","",O42/J42)</f>
         <v/>
       </c>
-      <c r="Q42" s="2" t="n"/>
+      <c r="Q42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="7" t="n"/>
-      <c r="I43" s="6" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="7" t="n"/>
+      <c r="A43" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="B43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン ココマーク 二つ折りコンパクト財布 黒 6962639 財布</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>45684</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>45693</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>19000</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>45707</v>
+      </c>
       <c r="L43" s="9">
         <f>IF(K43="","",K43-H43)</f>
         <v/>
       </c>
-      <c r="M43" s="8" t="n"/>
-      <c r="N43" s="8" t="n"/>
+      <c r="M43" s="8" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O43" s="8">
         <f>IF(J43="","",J43-G43-M43-N43)</f>
         <v/>
@@ -4575,26 +5221,60 @@
         <f>IF(J43="","",O43/J43)</f>
         <v/>
       </c>
-      <c r="Q43" s="6" t="n"/>
+      <c r="Q43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="3" t="n"/>
+      <c r="A44" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 財布 ウォレット レディース ブラック系 AU8214</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>45302</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>5611</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>45329</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>PayPay</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>13900</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>45523</v>
+      </c>
       <c r="L44" s="5">
         <f>IF(K44="","",K44-H44)</f>
         <v/>
       </c>
-      <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="M44" s="4" t="n">
+        <v>694</v>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>200</v>
+      </c>
       <c r="O44" s="4">
         <f>IF(J44="","",J44-G44-M44-N44)</f>
         <v/>
@@ -4603,26 +5283,60 @@
         <f>IF(J44="","",O44/J44)</f>
         <v/>
       </c>
-      <c r="Q44" s="2" t="n"/>
+      <c r="Q44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="6" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="7" t="n"/>
+      <c r="A45" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>バッグ</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL シャネル トートバッグ ココマーク キャビアスキン</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>45541</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>100100</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>45548</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>130000</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>45724</v>
+      </c>
       <c r="L45" s="9">
         <f>IF(K45="","",K45-H45)</f>
         <v/>
       </c>
-      <c r="M45" s="8" t="n"/>
-      <c r="N45" s="8" t="n"/>
+      <c r="M45" s="8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>750</v>
+      </c>
       <c r="O45" s="8">
         <f>IF(J45="","",J45-G45-M45-N45)</f>
         <v/>
@@ -4631,26 +5345,60 @@
         <f>IF(J45="","",O45/J45)</f>
         <v/>
       </c>
-      <c r="Q45" s="6" t="n"/>
+      <c r="Q45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="3" t="n"/>
+      <c r="A46" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL シャネル 正規品 ココマーク 型押し レザー ブラック 黒</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>45712</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>45719</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>19500</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>45725</v>
+      </c>
       <c r="L46" s="5">
         <f>IF(K46="","",K46-H46)</f>
         <v/>
       </c>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
+      <c r="M46" s="4" t="n">
+        <v>1950</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O46" s="4">
         <f>IF(J46="","",J46-G46-M46-N46)</f>
         <v/>
@@ -4659,26 +5407,60 @@
         <f>IF(J46="","",O46/J46)</f>
         <v/>
       </c>
-      <c r="Q46" s="2" t="n"/>
+      <c r="Q46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="6" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="7" t="n"/>
+      <c r="A47" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル キャビアスキン 長財布 3番台 財布</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>45686</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>7150</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>45693</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>15400</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>45727</v>
+      </c>
       <c r="L47" s="9">
         <f>IF(K47="","",K47-H47)</f>
         <v/>
       </c>
-      <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="M47" s="8" t="n">
+        <v>1540</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O47" s="8">
         <f>IF(J47="","",J47-G47-M47-N47)</f>
         <v/>
@@ -4687,26 +5469,60 @@
         <f>IF(J47="","",O47/J47)</f>
         <v/>
       </c>
-      <c r="Q47" s="6" t="n"/>
+      <c r="Q47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="3" t="n"/>
+      <c r="A48" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 財布 ウォレット 札入れ 小銭入れ レディース ブラック系 FF9347</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>45712</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>8328</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>45719</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>45732</v>
+      </c>
       <c r="L48" s="5">
         <f>IF(K48="","",K48-H48)</f>
         <v/>
       </c>
-      <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="M48" s="4" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O48" s="4">
         <f>IF(J48="","",J48-G48-M48-N48)</f>
         <v/>
@@ -4715,26 +5531,60 @@
         <f>IF(J48="","",O48/J48)</f>
         <v/>
       </c>
-      <c r="Q48" s="2" t="n"/>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="6" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="7" t="n"/>
+      <c r="A49" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>CHANE カメリア ラウンドファスナー長財布 ブラック 財布</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>45562</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>18700</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>45575</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="n">
+        <v>14950</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>45732</v>
+      </c>
       <c r="L49" s="9">
         <f>IF(K49="","",K49-H49)</f>
         <v/>
       </c>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
+      <c r="M49" s="8" t="n">
+        <v>1384</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>439</v>
+      </c>
       <c r="O49" s="8">
         <f>IF(J49="","",J49-G49-M49-N49)</f>
         <v/>
@@ -4743,26 +5593,60 @@
         <f>IF(J49="","",O49/J49)</f>
         <v/>
       </c>
-      <c r="Q49" s="6" t="n"/>
+      <c r="Q49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="3" t="n"/>
+      <c r="A50" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL マトラッセ ラウンドジップ 長財布</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>45364</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>31900</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>45378</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>29100</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>45732</v>
+      </c>
       <c r="L50" s="5">
         <f>IF(K50="","",K50-H50)</f>
         <v/>
       </c>
-      <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="M50" s="4" t="n">
+        <v>2799</v>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>439</v>
+      </c>
       <c r="O50" s="4">
         <f>IF(J50="","",J50-G50-M50-N50)</f>
         <v/>
@@ -4771,26 +5655,60 @@
         <f>IF(J50="","",O50/J50)</f>
         <v/>
       </c>
-      <c r="Q50" s="2" t="n"/>
+      <c r="Q50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="7" t="n"/>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="7" t="n"/>
+      <c r="A51" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL CHANEL 財布 長財布 ココマーク キャビアスキン ブラック レザー 財布</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>45730</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>45741</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>16900</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>45743</v>
+      </c>
       <c r="L51" s="9">
         <f>IF(K51="","",K51-H51)</f>
         <v/>
       </c>
-      <c r="M51" s="8" t="n"/>
-      <c r="N51" s="8" t="n"/>
+      <c r="M51" s="8" t="n">
+        <v>1690</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O51" s="8">
         <f>IF(J51="","",J51-G51-M51-N51)</f>
         <v/>
@@ -4799,26 +5717,60 @@
         <f>IF(J51="","",O51/J51)</f>
         <v/>
       </c>
-      <c r="Q51" s="6" t="n"/>
+      <c r="Q51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="3" t="n"/>
+      <c r="A52" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル ココマーク 財布 シール 財布</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>45665</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>45674</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>45744</v>
+      </c>
       <c r="L52" s="5">
         <f>IF(K52="","",K52-H52)</f>
         <v/>
       </c>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="M52" s="4" t="n">
+        <v>1840</v>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O52" s="4">
         <f>IF(J52="","",J52-G52-M52-N52)</f>
         <v/>
@@ -4827,26 +5779,60 @@
         <f>IF(J52="","",O52/J52)</f>
         <v/>
       </c>
-      <c r="Q52" s="2" t="n"/>
+      <c r="Q52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="n"/>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="7" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="7" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="7" t="n"/>
+      <c r="A53" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL キャビアスキン シャネル キャビアスキン 折財布 7番台 財布</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>45728</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>8253</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>45732</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="n">
+        <v>19100</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>45744</v>
+      </c>
       <c r="L53" s="9">
         <f>IF(K53="","",K53-H53)</f>
         <v/>
       </c>
-      <c r="M53" s="8" t="n"/>
-      <c r="N53" s="8" t="n"/>
+      <c r="M53" s="8" t="n">
+        <v>1910</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O53" s="8">
         <f>IF(J53="","",J53-G53-M53-N53)</f>
         <v/>
@@ -4855,26 +5841,60 @@
         <f>IF(J53="","",O53/J53)</f>
         <v/>
       </c>
-      <c r="Q53" s="6" t="n"/>
+      <c r="Q53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="3" t="n"/>
+      <c r="A54" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>✨CHANEL✨シャネル キャビアスキン 折り財布 箱付き</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>45727</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>45730</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>20900</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>45746</v>
+      </c>
       <c r="L54" s="5">
         <f>IF(K54="","",K54-H54)</f>
         <v/>
       </c>
-      <c r="M54" s="4" t="n"/>
-      <c r="N54" s="4" t="n"/>
+      <c r="M54" s="4" t="n">
+        <v>2090</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O54" s="4">
         <f>IF(J54="","",J54-G54-M54-N54)</f>
         <v/>
@@ -4883,26 +5903,60 @@
         <f>IF(J54="","",O54/J54)</f>
         <v/>
       </c>
-      <c r="Q54" s="2" t="n"/>
+      <c r="Q54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="n"/>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="6" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="7" t="n"/>
+      <c r="A55" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL カンボン カンボンライン マトラッセ 長財布</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>45750</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>9350</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>45754</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>45754</v>
+      </c>
       <c r="L55" s="9">
         <f>IF(K55="","",K55-H55)</f>
         <v/>
       </c>
-      <c r="M55" s="8" t="n"/>
-      <c r="N55" s="8" t="n"/>
+      <c r="M55" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O55" s="8">
         <f>IF(J55="","",J55-G55-M55-N55)</f>
         <v/>
@@ -4911,26 +5965,60 @@
         <f>IF(J55="","",O55/J55)</f>
         <v/>
       </c>
-      <c r="Q55" s="6" t="n"/>
+      <c r="Q55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="3" t="n"/>
+      <c r="A56" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL ラウンドジップ 21333425 財布</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>45352</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>60500</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>45358</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>71500</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>45770</v>
+      </c>
       <c r="L56" s="5">
         <f>IF(K56="","",K56-H56)</f>
         <v/>
       </c>
-      <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="M56" s="4" t="n">
+        <v>2640</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>800</v>
+      </c>
       <c r="O56" s="4">
         <f>IF(J56="","",J56-G56-M56-N56)</f>
         <v/>
@@ -4939,26 +6027,60 @@
         <f>IF(J56="","",O56/J56)</f>
         <v/>
       </c>
-      <c r="Q56" s="2" t="n"/>
+      <c r="Q56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="n"/>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="7" t="n"/>
-      <c r="I57" s="6" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="7" t="n"/>
+      <c r="A57" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="B57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 財布 ウォレット 札入れ 小銭入れ カード入れ ブラック系 FK4798</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>45727</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>8800</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>45731</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="n">
+        <v>15500</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>45772</v>
+      </c>
       <c r="L57" s="9">
         <f>IF(K57="","",K57-H57)</f>
         <v/>
       </c>
-      <c r="M57" s="8" t="n"/>
-      <c r="N57" s="8" t="n"/>
+      <c r="M57" s="8" t="n">
+        <v>1550</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O57" s="8">
         <f>IF(J57="","",J57-G57-M57-N57)</f>
         <v/>
@@ -4967,26 +6089,60 @@
         <f>IF(J57="","",O57/J57)</f>
         <v/>
       </c>
-      <c r="Q57" s="6" t="n"/>
+      <c r="Q57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="3" t="n"/>
+      <c r="A58" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 長財布 ウォレット 札入れ 小銭入れ レディース ブラック系 FK4857</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>45728</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>8525</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>45733</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="n">
+        <v>14700</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>45777</v>
+      </c>
       <c r="L58" s="5">
         <f>IF(K58="","",K58-H58)</f>
         <v/>
       </c>
-      <c r="M58" s="4" t="n"/>
-      <c r="N58" s="4" t="n"/>
+      <c r="M58" s="4" t="n">
+        <v>1470</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O58" s="4">
         <f>IF(J58="","",J58-G58-M58-N58)</f>
         <v/>
@@ -4995,26 +6151,60 @@
         <f>IF(J58="","",O58/J58)</f>
         <v/>
       </c>
-      <c r="Q58" s="2" t="n"/>
+      <c r="Q58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="n"/>
-      <c r="B59" s="6" t="n"/>
-      <c r="C59" s="6" t="n"/>
-      <c r="D59" s="6" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="6" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="7" t="n"/>
+      <c r="A59" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>LOUIS VUITTON M91573 ヴェルニ ヴィトン ヴェルニ ドットインフィニティ M91573 財布</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>45716</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>45723</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>35600</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>45777</v>
+      </c>
       <c r="L59" s="9">
         <f>IF(K59="","",K59-H59)</f>
         <v/>
       </c>
-      <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
+      <c r="M59" s="8" t="n">
+        <v>3560</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O59" s="8">
         <f>IF(J59="","",J59-G59-M59-N59)</f>
         <v/>
@@ -5023,26 +6213,60 @@
         <f>IF(J59="","",O59/J59)</f>
         <v/>
       </c>
-      <c r="Q59" s="6" t="n"/>
+      <c r="Q59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="3" t="n"/>
+      <c r="A60" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B60" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>バッグ</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL シャネル カンボン トートバッグ シール 9番台 トートバッグ</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>83600</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>45639</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>92400</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>45793</v>
+      </c>
       <c r="L60" s="5">
         <f>IF(K60="","",K60-H60)</f>
         <v/>
       </c>
-      <c r="M60" s="4" t="n"/>
-      <c r="N60" s="4" t="n"/>
+      <c r="M60" s="4" t="n">
+        <v>2640</v>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>1440</v>
+      </c>
       <c r="O60" s="4">
         <f>IF(J60="","",J60-G60-M60-N60)</f>
         <v/>
@@ -5051,26 +6275,60 @@
         <f>IF(J60="","",O60/J60)</f>
         <v/>
       </c>
-      <c r="Q60" s="2" t="n"/>
+      <c r="Q60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="n"/>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="6" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="7" t="n"/>
+      <c r="A61" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 長財布 ウォレット 小銭入れ 札入れ レディース ブラック系</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>45750</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>7975</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>45754</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>ラクマ</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>17800</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>45794</v>
+      </c>
       <c r="L61" s="9">
         <f>IF(K61="","",K61-H61)</f>
         <v/>
       </c>
-      <c r="M61" s="8" t="n"/>
-      <c r="N61" s="8" t="n"/>
+      <c r="M61" s="8" t="n">
+        <v>1780</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>200</v>
+      </c>
       <c r="O61" s="8">
         <f>IF(J61="","",J61-G61-M61-N61)</f>
         <v/>
@@ -5079,26 +6337,60 @@
         <f>IF(J61="","",O61/J61)</f>
         <v/>
       </c>
-      <c r="Q61" s="6" t="n"/>
+      <c r="Q61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="3" t="n"/>
+      <c r="A62" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 財布 ウォレット 札入れ 小銭入れ カード入れ レディース ブラック系</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>45732</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>6801</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>45738</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="n">
+        <v>16200</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>45798</v>
+      </c>
       <c r="L62" s="5">
         <f>IF(K62="","",K62-H62)</f>
         <v/>
       </c>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
+      <c r="M62" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O62" s="4">
         <f>IF(J62="","",J62-G62-M62-N62)</f>
         <v/>
@@ -5107,26 +6399,60 @@
         <f>IF(J62="","",O62/J62)</f>
         <v/>
       </c>
-      <c r="Q62" s="2" t="n"/>
+      <c r="Q62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="6" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="7" t="n"/>
+      <c r="A63" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 財布 ウォレット 札入れ 小銭入れ レディース ブラック系 FK5630</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>45732</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>6801</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>45737</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>15200</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>45800</v>
+      </c>
       <c r="L63" s="9">
         <f>IF(K63="","",K63-H63)</f>
         <v/>
       </c>
-      <c r="M63" s="8" t="n"/>
-      <c r="N63" s="8" t="n"/>
+      <c r="M63" s="8" t="n">
+        <v>1520</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O63" s="8">
         <f>IF(J63="","",J63-G63-M63-N63)</f>
         <v/>
@@ -5135,26 +6461,60 @@
         <f>IF(J63="","",O63/J63)</f>
         <v/>
       </c>
-      <c r="Q63" s="6" t="n"/>
+      <c r="Q63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="3" t="n"/>
+      <c r="A64" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B64" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL シャネル カンボンライン 長財布 9738299 財布</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>45805</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>9350</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>45817</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>45823</v>
+      </c>
       <c r="L64" s="5">
         <f>IF(K64="","",K64-H64)</f>
         <v/>
       </c>
-      <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
+      <c r="M64" s="4" t="n">
+        <v>1700</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>210</v>
+      </c>
       <c r="O64" s="4">
         <f>IF(J64="","",J64-G64-M64-N64)</f>
         <v/>
@@ -5163,26 +6523,60 @@
         <f>IF(J64="","",O64/J64)</f>
         <v/>
       </c>
-      <c r="Q64" s="2" t="n"/>
+      <c r="Q64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="7" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="8" t="n"/>
-      <c r="K65" s="7" t="n"/>
+      <c r="A65" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>CHANEL シャネル 2つ折り長財布 箱 ギャラ 財布</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>エコリング</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>45820</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>9350</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>45824</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="n">
+        <v>22500</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>45824</v>
+      </c>
       <c r="L65" s="9">
         <f>IF(K65="","",K65-H65)</f>
         <v/>
       </c>
-      <c r="M65" s="8" t="n"/>
-      <c r="N65" s="8" t="n"/>
+      <c r="M65" s="8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="N65" s="8" t="n">
+        <v>210</v>
+      </c>
       <c r="O65" s="8">
         <f>IF(J65="","",J65-G65-M65-N65)</f>
         <v/>
@@ -5191,26 +6585,60 @@
         <f>IF(J65="","",O65/J65)</f>
         <v/>
       </c>
-      <c r="Q65" s="6" t="n"/>
+      <c r="Q65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="3" t="n"/>
+      <c r="A66" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B66" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>CHANEL ココマーク キャビアスキン 財布 二つ折り ブラック</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>メルカリ</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>45713</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>45719</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>6861</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>45837</v>
+      </c>
       <c r="L66" s="5">
         <f>IF(K66="","",K66-H66)</f>
         <v/>
       </c>
-      <c r="M66" s="4" t="n"/>
-      <c r="N66" s="4" t="n"/>
+      <c r="M66" s="4" t="n">
+        <v>686</v>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>850</v>
+      </c>
       <c r="O66" s="4">
         <f>IF(J66="","",J66-G66-M66-N66)</f>
         <v/>
@@ -5219,26 +6647,60 @@
         <f>IF(J66="","",O66/J66)</f>
         <v/>
       </c>
-      <c r="Q66" s="2" t="n"/>
+      <c r="Q66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="8" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="6" t="n"/>
-      <c r="J67" s="8" t="n"/>
-      <c r="K67" s="7" t="n"/>
+      <c r="A67" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>財布</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>1円 CHANEL シャネル ココマーク キャビアスキン 二つ折り 財布 ウォレット 札入れ 小銭入れ カード入れ レディース ブラック系 FK6346</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>45732</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>6801</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>45737</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>ヤフオク</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>6861</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>45837</v>
+      </c>
       <c r="L67" s="9">
         <f>IF(K67="","",K67-H67)</f>
         <v/>
       </c>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
+      <c r="M67" s="8" t="n">
+        <v>1372</v>
+      </c>
+      <c r="N67" s="8" t="n">
+        <v>850</v>
+      </c>
       <c r="O67" s="8">
         <f>IF(J67="","",J67-G67-M67-N67)</f>
         <v/>
@@ -5247,7 +6709,7 @@
         <f>IF(J67="","",O67/J67)</f>
         <v/>
       </c>
-      <c r="Q67" s="6" t="n"/>
+      <c r="Q67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>

--- a/管理スプレッドシート.xlsx
+++ b/管理スプレッドシート.xlsx
@@ -11,7 +11,7 @@
     <sheet name="販売済" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'未販売'!$A$1:$J$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'未販売'!$A$1:$P$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'販売済'!$A$1:$Q$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,13 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="25" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -558,6 +564,36 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>販売先</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>販売予定価格</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>想定手数料</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>送料</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>想定利益</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>利益判定</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>メモ</t>
         </is>
       </c>
@@ -597,7 +633,19 @@
         <f>IF(H2="","",TODAY()-H2)</f>
         <v/>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4">
+        <f>IF(K2="","",K2-G2-L2-M2)</f>
+        <v/>
+      </c>
+      <c r="O2" s="12">
+        <f>IF(N2="","",IF(N2&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -634,7 +682,19 @@
         <f>IF(H3="","",TODAY()-H3)</f>
         <v/>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8">
+        <f>IF(K3="","",K3-G3-L3-M3)</f>
+        <v/>
+      </c>
+      <c r="O3" s="13">
+        <f>IF(N3="","",IF(N3&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>ギャラ＋保存袋</t>
         </is>
@@ -675,7 +735,19 @@
         <f>IF(H4="","",TODAY()-H4)</f>
         <v/>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4">
+        <f>IF(K4="","",K4-G4-L4-M4)</f>
+        <v/>
+      </c>
+      <c r="O4" s="12">
+        <f>IF(N4="","",IF(N4&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>ギャラ＋保存袋＋箱</t>
         </is>
@@ -716,7 +788,19 @@
         <f>IF(H5="","",TODAY()-H5)</f>
         <v/>
       </c>
-      <c r="J5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+      <c r="M5" s="8" t="n"/>
+      <c r="N5" s="8">
+        <f>IF(K5="","",K5-G5-L5-M5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="13">
+        <f>IF(N5="","",IF(N5&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -753,7 +837,19 @@
         <f>IF(H6="","",TODAY()-H6)</f>
         <v/>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4">
+        <f>IF(K6="","",K6-G6-L6-M6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>IF(N6="","",IF(N6&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -790,7 +886,19 @@
         <f>IF(H7="","",TODAY()-H7)</f>
         <v/>
       </c>
-      <c r="J7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8">
+        <f>IF(K7="","",K7-G7-L7-M7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="13">
+        <f>IF(N7="","",IF(N7&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -827,7 +935,19 @@
         <f>IF(H8="","",TODAY()-H8)</f>
         <v/>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4">
+        <f>IF(K8="","",K8-G8-L8-M8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>IF(N8="","",IF(N8&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -864,7 +984,19 @@
         <f>IF(H9="","",TODAY()-H9)</f>
         <v/>
       </c>
-      <c r="J9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8">
+        <f>IF(K9="","",K9-G9-L9-M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="13">
+        <f>IF(N9="","",IF(N9&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -901,7 +1033,19 @@
         <f>IF(H10="","",TODAY()-H10)</f>
         <v/>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4">
+        <f>IF(K10="","",K10-G10-L10-M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="12">
+        <f>IF(N10="","",IF(N10&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>箱あり</t>
         </is>
@@ -942,7 +1086,19 @@
         <f>IF(H11="","",TODAY()-H11)</f>
         <v/>
       </c>
-      <c r="J11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8">
+        <f>IF(K11="","",K11-G11-L11-M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="13">
+        <f>IF(N11="","",IF(N11&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -979,7 +1135,19 @@
         <f>IF(H12="","",TODAY()-H12)</f>
         <v/>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4">
+        <f>IF(K12="","",K12-G12-L12-M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="12">
+        <f>IF(N12="","",IF(N12&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1016,7 +1184,19 @@
         <f>IF(H13="","",TODAY()-H13)</f>
         <v/>
       </c>
-      <c r="J13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8">
+        <f>IF(K13="","",K13-G13-L13-M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="13">
+        <f>IF(N13="","",IF(N13&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1053,7 +1233,19 @@
         <f>IF(H14="","",TODAY()-H14)</f>
         <v/>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4">
+        <f>IF(K14="","",K14-G14-L14-M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="12">
+        <f>IF(N14="","",IF(N14&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>箱あり</t>
         </is>
@@ -1094,7 +1286,19 @@
         <f>IF(H15="","",TODAY()-H15)</f>
         <v/>
       </c>
-      <c r="J15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="8" t="n"/>
+      <c r="N15" s="8">
+        <f>IF(K15="","",K15-G15-L15-M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="13">
+        <f>IF(N15="","",IF(N15&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1131,7 +1335,19 @@
         <f>IF(H16="","",TODAY()-H16)</f>
         <v/>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4">
+        <f>IF(K16="","",K16-G16-L16-M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="12">
+        <f>IF(N16="","",IF(N16&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1168,7 +1384,19 @@
         <f>IF(H17="","",TODAY()-H17)</f>
         <v/>
       </c>
-      <c r="J17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8">
+        <f>IF(K17="","",K17-G17-L17-M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="13">
+        <f>IF(N17="","",IF(N17&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1205,7 +1433,19 @@
         <f>IF(H18="","",TODAY()-H18)</f>
         <v/>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4">
+        <f>IF(K18="","",K18-G18-L18-M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="12">
+        <f>IF(N18="","",IF(N18&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1242,7 +1482,19 @@
         <f>IF(H19="","",TODAY()-H19)</f>
         <v/>
       </c>
-      <c r="J19" s="6" t="inlineStr"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8">
+        <f>IF(K19="","",K19-G19-L19-M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="13">
+        <f>IF(N19="","",IF(N19&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1258,6 +1510,18 @@
         <v/>
       </c>
       <c r="J20" s="2" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4">
+        <f>IF(K20="","",K20-G20-L20-M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="12">
+        <f>IF(N20="","",IF(N20&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1273,6 +1537,18 @@
         <v/>
       </c>
       <c r="J21" s="6" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8">
+        <f>IF(K21="","",K21-G21-L21-M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="13">
+        <f>IF(N21="","",IF(N21&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1288,6 +1564,18 @@
         <v/>
       </c>
       <c r="J22" s="2" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4">
+        <f>IF(K22="","",K22-G22-L22-M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="12">
+        <f>IF(N22="","",IF(N22&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1303,6 +1591,18 @@
         <v/>
       </c>
       <c r="J23" s="6" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8">
+        <f>IF(K23="","",K23-G23-L23-M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="13">
+        <f>IF(N23="","",IF(N23&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1318,6 +1618,18 @@
         <v/>
       </c>
       <c r="J24" s="2" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4">
+        <f>IF(K24="","",K24-G24-L24-M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="12">
+        <f>IF(N24="","",IF(N24&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1333,6 +1645,18 @@
         <v/>
       </c>
       <c r="J25" s="6" t="n"/>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="8">
+        <f>IF(K25="","",K25-G25-L25-M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="13">
+        <f>IF(N25="","",IF(N25&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1348,6 +1672,18 @@
         <v/>
       </c>
       <c r="J26" s="2" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4">
+        <f>IF(K26="","",K26-G26-L26-M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="12">
+        <f>IF(N26="","",IF(N26&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1363,6 +1699,18 @@
         <v/>
       </c>
       <c r="J27" s="6" t="n"/>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="8" t="n"/>
+      <c r="N27" s="8">
+        <f>IF(K27="","",K27-G27-L27-M27)</f>
+        <v/>
+      </c>
+      <c r="O27" s="13">
+        <f>IF(N27="","",IF(N27&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -1378,6 +1726,18 @@
         <v/>
       </c>
       <c r="J28" s="2" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4">
+        <f>IF(K28="","",K28-G28-L28-M28)</f>
+        <v/>
+      </c>
+      <c r="O28" s="12">
+        <f>IF(N28="","",IF(N28&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1393,6 +1753,18 @@
         <v/>
       </c>
       <c r="J29" s="6" t="n"/>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="8" t="n"/>
+      <c r="N29" s="8">
+        <f>IF(K29="","",K29-G29-L29-M29)</f>
+        <v/>
+      </c>
+      <c r="O29" s="13">
+        <f>IF(N29="","",IF(N29&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -1408,6 +1780,18 @@
         <v/>
       </c>
       <c r="J30" s="2" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4">
+        <f>IF(K30="","",K30-G30-L30-M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="12">
+        <f>IF(N30="","",IF(N30&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1423,6 +1807,18 @@
         <v/>
       </c>
       <c r="J31" s="6" t="n"/>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="8" t="n"/>
+      <c r="N31" s="8">
+        <f>IF(K31="","",K31-G31-L31-M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="13">
+        <f>IF(N31="","",IF(N31&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -1438,6 +1834,18 @@
         <v/>
       </c>
       <c r="J32" s="2" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4">
+        <f>IF(K32="","",K32-G32-L32-M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="12">
+        <f>IF(N32="","",IF(N32&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1453,6 +1861,18 @@
         <v/>
       </c>
       <c r="J33" s="6" t="n"/>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="8" t="n"/>
+      <c r="N33" s="8">
+        <f>IF(K33="","",K33-G33-L33-M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="13">
+        <f>IF(N33="","",IF(N33&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -1468,6 +1888,18 @@
         <v/>
       </c>
       <c r="J34" s="2" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4">
+        <f>IF(K34="","",K34-G34-L34-M34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="12">
+        <f>IF(N34="","",IF(N34&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1483,6 +1915,18 @@
         <v/>
       </c>
       <c r="J35" s="6" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="8">
+        <f>IF(K35="","",K35-G35-L35-M35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="13">
+        <f>IF(N35="","",IF(N35&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -1498,6 +1942,18 @@
         <v/>
       </c>
       <c r="J36" s="2" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4">
+        <f>IF(K36="","",K36-G36-L36-M36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="12">
+        <f>IF(N36="","",IF(N36&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1513,6 +1969,18 @@
         <v/>
       </c>
       <c r="J37" s="6" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="8">
+        <f>IF(K37="","",K37-G37-L37-M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="13">
+        <f>IF(N37="","",IF(N37&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -1528,6 +1996,18 @@
         <v/>
       </c>
       <c r="J38" s="2" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4">
+        <f>IF(K38="","",K38-G38-L38-M38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="12">
+        <f>IF(N38="","",IF(N38&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1543,6 +2023,18 @@
         <v/>
       </c>
       <c r="J39" s="6" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="8">
+        <f>IF(K39="","",K39-G39-L39-M39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="13">
+        <f>IF(N39="","",IF(N39&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -1558,6 +2050,18 @@
         <v/>
       </c>
       <c r="J40" s="2" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4">
+        <f>IF(K40="","",K40-G40-L40-M40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="12">
+        <f>IF(N40="","",IF(N40&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1573,6 +2077,18 @@
         <v/>
       </c>
       <c r="J41" s="6" t="n"/>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="8" t="n"/>
+      <c r="N41" s="8">
+        <f>IF(K41="","",K41-G41-L41-M41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="13">
+        <f>IF(N41="","",IF(N41&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -1588,6 +2104,18 @@
         <v/>
       </c>
       <c r="J42" s="2" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4">
+        <f>IF(K42="","",K42-G42-L42-M42)</f>
+        <v/>
+      </c>
+      <c r="O42" s="12">
+        <f>IF(N42="","",IF(N42&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1603,6 +2131,18 @@
         <v/>
       </c>
       <c r="J43" s="6" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8">
+        <f>IF(K43="","",K43-G43-L43-M43)</f>
+        <v/>
+      </c>
+      <c r="O43" s="13">
+        <f>IF(N43="","",IF(N43&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -1618,6 +2158,18 @@
         <v/>
       </c>
       <c r="J44" s="2" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4">
+        <f>IF(K44="","",K44-G44-L44-M44)</f>
+        <v/>
+      </c>
+      <c r="O44" s="12">
+        <f>IF(N44="","",IF(N44&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1633,6 +2185,18 @@
         <v/>
       </c>
       <c r="J45" s="6" t="n"/>
+      <c r="K45" s="8" t="n"/>
+      <c r="L45" s="8" t="n"/>
+      <c r="M45" s="8" t="n"/>
+      <c r="N45" s="8">
+        <f>IF(K45="","",K45-G45-L45-M45)</f>
+        <v/>
+      </c>
+      <c r="O45" s="13">
+        <f>IF(N45="","",IF(N45&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -1648,6 +2212,18 @@
         <v/>
       </c>
       <c r="J46" s="2" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4">
+        <f>IF(K46="","",K46-G46-L46-M46)</f>
+        <v/>
+      </c>
+      <c r="O46" s="12">
+        <f>IF(N46="","",IF(N46&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1663,6 +2239,18 @@
         <v/>
       </c>
       <c r="J47" s="6" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="8" t="n"/>
+      <c r="N47" s="8">
+        <f>IF(K47="","",K47-G47-L47-M47)</f>
+        <v/>
+      </c>
+      <c r="O47" s="13">
+        <f>IF(N47="","",IF(N47&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -1678,6 +2266,18 @@
         <v/>
       </c>
       <c r="J48" s="2" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4">
+        <f>IF(K48="","",K48-G48-L48-M48)</f>
+        <v/>
+      </c>
+      <c r="O48" s="12">
+        <f>IF(N48="","",IF(N48&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1693,6 +2293,18 @@
         <v/>
       </c>
       <c r="J49" s="6" t="n"/>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="8" t="n"/>
+      <c r="N49" s="8">
+        <f>IF(K49="","",K49-G49-L49-M49)</f>
+        <v/>
+      </c>
+      <c r="O49" s="13">
+        <f>IF(N49="","",IF(N49&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -1708,6 +2320,18 @@
         <v/>
       </c>
       <c r="J50" s="2" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4">
+        <f>IF(K50="","",K50-G50-L50-M50)</f>
+        <v/>
+      </c>
+      <c r="O50" s="12">
+        <f>IF(N50="","",IF(N50&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1723,6 +2347,18 @@
         <v/>
       </c>
       <c r="J51" s="6" t="n"/>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="8" t="n"/>
+      <c r="N51" s="8">
+        <f>IF(K51="","",K51-G51-L51-M51)</f>
+        <v/>
+      </c>
+      <c r="O51" s="13">
+        <f>IF(N51="","",IF(N51&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -1738,6 +2374,18 @@
         <v/>
       </c>
       <c r="J52" s="2" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4">
+        <f>IF(K52="","",K52-G52-L52-M52)</f>
+        <v/>
+      </c>
+      <c r="O52" s="12">
+        <f>IF(N52="","",IF(N52&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1753,6 +2401,18 @@
         <v/>
       </c>
       <c r="J53" s="6" t="n"/>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="8" t="n"/>
+      <c r="N53" s="8">
+        <f>IF(K53="","",K53-G53-L53-M53)</f>
+        <v/>
+      </c>
+      <c r="O53" s="13">
+        <f>IF(N53="","",IF(N53&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -1768,6 +2428,18 @@
         <v/>
       </c>
       <c r="J54" s="2" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4">
+        <f>IF(K54="","",K54-G54-L54-M54)</f>
+        <v/>
+      </c>
+      <c r="O54" s="12">
+        <f>IF(N54="","",IF(N54&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1783,6 +2455,18 @@
         <v/>
       </c>
       <c r="J55" s="6" t="n"/>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="8" t="n"/>
+      <c r="N55" s="8">
+        <f>IF(K55="","",K55-G55-L55-M55)</f>
+        <v/>
+      </c>
+      <c r="O55" s="13">
+        <f>IF(N55="","",IF(N55&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -1798,6 +2482,18 @@
         <v/>
       </c>
       <c r="J56" s="2" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4">
+        <f>IF(K56="","",K56-G56-L56-M56)</f>
+        <v/>
+      </c>
+      <c r="O56" s="12">
+        <f>IF(N56="","",IF(N56&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1813,6 +2509,18 @@
         <v/>
       </c>
       <c r="J57" s="6" t="n"/>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="8" t="n"/>
+      <c r="N57" s="8">
+        <f>IF(K57="","",K57-G57-L57-M57)</f>
+        <v/>
+      </c>
+      <c r="O57" s="13">
+        <f>IF(N57="","",IF(N57&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -1828,6 +2536,18 @@
         <v/>
       </c>
       <c r="J58" s="2" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4">
+        <f>IF(K58="","",K58-G58-L58-M58)</f>
+        <v/>
+      </c>
+      <c r="O58" s="12">
+        <f>IF(N58="","",IF(N58&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1843,6 +2563,18 @@
         <v/>
       </c>
       <c r="J59" s="6" t="n"/>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="8" t="n"/>
+      <c r="N59" s="8">
+        <f>IF(K59="","",K59-G59-L59-M59)</f>
+        <v/>
+      </c>
+      <c r="O59" s="13">
+        <f>IF(N59="","",IF(N59&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -1858,6 +2590,18 @@
         <v/>
       </c>
       <c r="J60" s="2" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4">
+        <f>IF(K60="","",K60-G60-L60-M60)</f>
+        <v/>
+      </c>
+      <c r="O60" s="12">
+        <f>IF(N60="","",IF(N60&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -1873,6 +2617,18 @@
         <v/>
       </c>
       <c r="J61" s="6" t="n"/>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
+      <c r="M61" s="8" t="n"/>
+      <c r="N61" s="8">
+        <f>IF(K61="","",K61-G61-L61-M61)</f>
+        <v/>
+      </c>
+      <c r="O61" s="13">
+        <f>IF(N61="","",IF(N61&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -1888,6 +2644,18 @@
         <v/>
       </c>
       <c r="J62" s="2" t="n"/>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="n"/>
+      <c r="N62" s="4">
+        <f>IF(K62="","",K62-G62-L62-M62)</f>
+        <v/>
+      </c>
+      <c r="O62" s="12">
+        <f>IF(N62="","",IF(N62&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -1903,6 +2671,18 @@
         <v/>
       </c>
       <c r="J63" s="6" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
+      <c r="N63" s="8">
+        <f>IF(K63="","",K63-G63-L63-M63)</f>
+        <v/>
+      </c>
+      <c r="O63" s="13">
+        <f>IF(N63="","",IF(N63&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -1918,6 +2698,18 @@
         <v/>
       </c>
       <c r="J64" s="2" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4">
+        <f>IF(K64="","",K64-G64-L64-M64)</f>
+        <v/>
+      </c>
+      <c r="O64" s="12">
+        <f>IF(N64="","",IF(N64&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -1933,6 +2725,18 @@
         <v/>
       </c>
       <c r="J65" s="6" t="n"/>
+      <c r="K65" s="8" t="n"/>
+      <c r="L65" s="8" t="n"/>
+      <c r="M65" s="8" t="n"/>
+      <c r="N65" s="8">
+        <f>IF(K65="","",K65-G65-L65-M65)</f>
+        <v/>
+      </c>
+      <c r="O65" s="13">
+        <f>IF(N65="","",IF(N65&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -1948,6 +2752,18 @@
         <v/>
       </c>
       <c r="J66" s="2" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4">
+        <f>IF(K66="","",K66-G66-L66-M66)</f>
+        <v/>
+      </c>
+      <c r="O66" s="12">
+        <f>IF(N66="","",IF(N66&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -1963,6 +2779,18 @@
         <v/>
       </c>
       <c r="J67" s="6" t="n"/>
+      <c r="K67" s="8" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="8">
+        <f>IF(K67="","",K67-G67-L67-M67)</f>
+        <v/>
+      </c>
+      <c r="O67" s="13">
+        <f>IF(N67="","",IF(N67&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -1978,6 +2806,18 @@
         <v/>
       </c>
       <c r="J68" s="2" t="n"/>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4">
+        <f>IF(K68="","",K68-G68-L68-M68)</f>
+        <v/>
+      </c>
+      <c r="O68" s="12">
+        <f>IF(N68="","",IF(N68&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -1993,6 +2833,18 @@
         <v/>
       </c>
       <c r="J69" s="6" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="8">
+        <f>IF(K69="","",K69-G69-L69-M69)</f>
+        <v/>
+      </c>
+      <c r="O69" s="13">
+        <f>IF(N69="","",IF(N69&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -2008,6 +2860,18 @@
         <v/>
       </c>
       <c r="J70" s="2" t="n"/>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4">
+        <f>IF(K70="","",K70-G70-L70-M70)</f>
+        <v/>
+      </c>
+      <c r="O70" s="12">
+        <f>IF(N70="","",IF(N70&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -2023,6 +2887,18 @@
         <v/>
       </c>
       <c r="J71" s="6" t="n"/>
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
+      <c r="N71" s="8">
+        <f>IF(K71="","",K71-G71-L71-M71)</f>
+        <v/>
+      </c>
+      <c r="O71" s="13">
+        <f>IF(N71="","",IF(N71&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -2038,6 +2914,18 @@
         <v/>
       </c>
       <c r="J72" s="2" t="n"/>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4">
+        <f>IF(K72="","",K72-G72-L72-M72)</f>
+        <v/>
+      </c>
+      <c r="O72" s="12">
+        <f>IF(N72="","",IF(N72&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -2053,6 +2941,18 @@
         <v/>
       </c>
       <c r="J73" s="6" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
+      <c r="N73" s="8">
+        <f>IF(K73="","",K73-G73-L73-M73)</f>
+        <v/>
+      </c>
+      <c r="O73" s="13">
+        <f>IF(N73="","",IF(N73&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -2068,6 +2968,18 @@
         <v/>
       </c>
       <c r="J74" s="2" t="n"/>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4">
+        <f>IF(K74="","",K74-G74-L74-M74)</f>
+        <v/>
+      </c>
+      <c r="O74" s="12">
+        <f>IF(N74="","",IF(N74&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -2083,6 +2995,18 @@
         <v/>
       </c>
       <c r="J75" s="6" t="n"/>
+      <c r="K75" s="8" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="8" t="n"/>
+      <c r="N75" s="8">
+        <f>IF(K75="","",K75-G75-L75-M75)</f>
+        <v/>
+      </c>
+      <c r="O75" s="13">
+        <f>IF(N75="","",IF(N75&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -2098,6 +3022,18 @@
         <v/>
       </c>
       <c r="J76" s="2" t="n"/>
+      <c r="K76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4">
+        <f>IF(K76="","",K76-G76-L76-M76)</f>
+        <v/>
+      </c>
+      <c r="O76" s="12">
+        <f>IF(N76="","",IF(N76&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -2113,6 +3049,18 @@
         <v/>
       </c>
       <c r="J77" s="6" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="8">
+        <f>IF(K77="","",K77-G77-L77-M77)</f>
+        <v/>
+      </c>
+      <c r="O77" s="13">
+        <f>IF(N77="","",IF(N77&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -2128,6 +3076,18 @@
         <v/>
       </c>
       <c r="J78" s="2" t="n"/>
+      <c r="K78" s="4" t="n"/>
+      <c r="L78" s="4" t="n"/>
+      <c r="M78" s="4" t="n"/>
+      <c r="N78" s="4">
+        <f>IF(K78="","",K78-G78-L78-M78)</f>
+        <v/>
+      </c>
+      <c r="O78" s="12">
+        <f>IF(N78="","",IF(N78&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -2143,6 +3103,18 @@
         <v/>
       </c>
       <c r="J79" s="6" t="n"/>
+      <c r="K79" s="8" t="n"/>
+      <c r="L79" s="8" t="n"/>
+      <c r="M79" s="8" t="n"/>
+      <c r="N79" s="8">
+        <f>IF(K79="","",K79-G79-L79-M79)</f>
+        <v/>
+      </c>
+      <c r="O79" s="13">
+        <f>IF(N79="","",IF(N79&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -2158,6 +3130,18 @@
         <v/>
       </c>
       <c r="J80" s="2" t="n"/>
+      <c r="K80" s="4" t="n"/>
+      <c r="L80" s="4" t="n"/>
+      <c r="M80" s="4" t="n"/>
+      <c r="N80" s="4">
+        <f>IF(K80="","",K80-G80-L80-M80)</f>
+        <v/>
+      </c>
+      <c r="O80" s="12">
+        <f>IF(N80="","",IF(N80&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -2173,6 +3157,18 @@
         <v/>
       </c>
       <c r="J81" s="6" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
+      <c r="N81" s="8">
+        <f>IF(K81="","",K81-G81-L81-M81)</f>
+        <v/>
+      </c>
+      <c r="O81" s="13">
+        <f>IF(N81="","",IF(N81&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -2188,6 +3184,18 @@
         <v/>
       </c>
       <c r="J82" s="2" t="n"/>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="n"/>
+      <c r="N82" s="4">
+        <f>IF(K82="","",K82-G82-L82-M82)</f>
+        <v/>
+      </c>
+      <c r="O82" s="12">
+        <f>IF(N82="","",IF(N82&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -2203,6 +3211,18 @@
         <v/>
       </c>
       <c r="J83" s="6" t="n"/>
+      <c r="K83" s="8" t="n"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="8" t="n"/>
+      <c r="N83" s="8">
+        <f>IF(K83="","",K83-G83-L83-M83)</f>
+        <v/>
+      </c>
+      <c r="O83" s="13">
+        <f>IF(N83="","",IF(N83&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -2218,6 +3238,18 @@
         <v/>
       </c>
       <c r="J84" s="2" t="n"/>
+      <c r="K84" s="4" t="n"/>
+      <c r="L84" s="4" t="n"/>
+      <c r="M84" s="4" t="n"/>
+      <c r="N84" s="4">
+        <f>IF(K84="","",K84-G84-L84-M84)</f>
+        <v/>
+      </c>
+      <c r="O84" s="12">
+        <f>IF(N84="","",IF(N84&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -2233,6 +3265,18 @@
         <v/>
       </c>
       <c r="J85" s="6" t="n"/>
+      <c r="K85" s="8" t="n"/>
+      <c r="L85" s="8" t="n"/>
+      <c r="M85" s="8" t="n"/>
+      <c r="N85" s="8">
+        <f>IF(K85="","",K85-G85-L85-M85)</f>
+        <v/>
+      </c>
+      <c r="O85" s="13">
+        <f>IF(N85="","",IF(N85&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -2248,6 +3292,18 @@
         <v/>
       </c>
       <c r="J86" s="2" t="n"/>
+      <c r="K86" s="4" t="n"/>
+      <c r="L86" s="4" t="n"/>
+      <c r="M86" s="4" t="n"/>
+      <c r="N86" s="4">
+        <f>IF(K86="","",K86-G86-L86-M86)</f>
+        <v/>
+      </c>
+      <c r="O86" s="12">
+        <f>IF(N86="","",IF(N86&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -2263,6 +3319,18 @@
         <v/>
       </c>
       <c r="J87" s="6" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
+      <c r="N87" s="8">
+        <f>IF(K87="","",K87-G87-L87-M87)</f>
+        <v/>
+      </c>
+      <c r="O87" s="13">
+        <f>IF(N87="","",IF(N87&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -2278,6 +3346,18 @@
         <v/>
       </c>
       <c r="J88" s="2" t="n"/>
+      <c r="K88" s="4" t="n"/>
+      <c r="L88" s="4" t="n"/>
+      <c r="M88" s="4" t="n"/>
+      <c r="N88" s="4">
+        <f>IF(K88="","",K88-G88-L88-M88)</f>
+        <v/>
+      </c>
+      <c r="O88" s="12">
+        <f>IF(N88="","",IF(N88&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -2293,6 +3373,18 @@
         <v/>
       </c>
       <c r="J89" s="6" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="8">
+        <f>IF(K89="","",K89-G89-L89-M89)</f>
+        <v/>
+      </c>
+      <c r="O89" s="13">
+        <f>IF(N89="","",IF(N89&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -2308,6 +3400,18 @@
         <v/>
       </c>
       <c r="J90" s="2" t="n"/>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4">
+        <f>IF(K90="","",K90-G90-L90-M90)</f>
+        <v/>
+      </c>
+      <c r="O90" s="12">
+        <f>IF(N90="","",IF(N90&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -2323,6 +3427,18 @@
         <v/>
       </c>
       <c r="J91" s="6" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+      <c r="N91" s="8">
+        <f>IF(K91="","",K91-G91-L91-M91)</f>
+        <v/>
+      </c>
+      <c r="O91" s="13">
+        <f>IF(N91="","",IF(N91&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -2338,6 +3454,18 @@
         <v/>
       </c>
       <c r="J92" s="2" t="n"/>
+      <c r="K92" s="4" t="n"/>
+      <c r="L92" s="4" t="n"/>
+      <c r="M92" s="4" t="n"/>
+      <c r="N92" s="4">
+        <f>IF(K92="","",K92-G92-L92-M92)</f>
+        <v/>
+      </c>
+      <c r="O92" s="12">
+        <f>IF(N92="","",IF(N92&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -2353,6 +3481,18 @@
         <v/>
       </c>
       <c r="J93" s="6" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+      <c r="N93" s="8">
+        <f>IF(K93="","",K93-G93-L93-M93)</f>
+        <v/>
+      </c>
+      <c r="O93" s="13">
+        <f>IF(N93="","",IF(N93&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -2368,6 +3508,18 @@
         <v/>
       </c>
       <c r="J94" s="2" t="n"/>
+      <c r="K94" s="4" t="n"/>
+      <c r="L94" s="4" t="n"/>
+      <c r="M94" s="4" t="n"/>
+      <c r="N94" s="4">
+        <f>IF(K94="","",K94-G94-L94-M94)</f>
+        <v/>
+      </c>
+      <c r="O94" s="12">
+        <f>IF(N94="","",IF(N94&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -2383,6 +3535,18 @@
         <v/>
       </c>
       <c r="J95" s="6" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
+      <c r="N95" s="8">
+        <f>IF(K95="","",K95-G95-L95-M95)</f>
+        <v/>
+      </c>
+      <c r="O95" s="13">
+        <f>IF(N95="","",IF(N95&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -2398,6 +3562,18 @@
         <v/>
       </c>
       <c r="J96" s="2" t="n"/>
+      <c r="K96" s="4" t="n"/>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="4" t="n"/>
+      <c r="N96" s="4">
+        <f>IF(K96="","",K96-G96-L96-M96)</f>
+        <v/>
+      </c>
+      <c r="O96" s="12">
+        <f>IF(N96="","",IF(N96&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -2413,6 +3589,18 @@
         <v/>
       </c>
       <c r="J97" s="6" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+      <c r="N97" s="8">
+        <f>IF(K97="","",K97-G97-L97-M97)</f>
+        <v/>
+      </c>
+      <c r="O97" s="13">
+        <f>IF(N97="","",IF(N97&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -2428,6 +3616,18 @@
         <v/>
       </c>
       <c r="J98" s="2" t="n"/>
+      <c r="K98" s="4" t="n"/>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="4" t="n"/>
+      <c r="N98" s="4">
+        <f>IF(K98="","",K98-G98-L98-M98)</f>
+        <v/>
+      </c>
+      <c r="O98" s="12">
+        <f>IF(N98="","",IF(N98&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -2443,6 +3643,18 @@
         <v/>
       </c>
       <c r="J99" s="6" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
+      <c r="N99" s="8">
+        <f>IF(K99="","",K99-G99-L99-M99)</f>
+        <v/>
+      </c>
+      <c r="O99" s="13">
+        <f>IF(N99="","",IF(N99&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -2458,6 +3670,18 @@
         <v/>
       </c>
       <c r="J100" s="2" t="n"/>
+      <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="n"/>
+      <c r="N100" s="4">
+        <f>IF(K100="","",K100-G100-L100-M100)</f>
+        <v/>
+      </c>
+      <c r="O100" s="12">
+        <f>IF(N100="","",IF(N100&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -2473,15 +3697,30 @@
         <v/>
       </c>
       <c r="J101" s="6" t="n"/>
+      <c r="K101" s="8" t="n"/>
+      <c r="L101" s="8" t="n"/>
+      <c r="M101" s="8" t="n"/>
+      <c r="N101" s="8">
+        <f>IF(K101="","",K101-G101-L101-M101)</f>
+        <v/>
+      </c>
+      <c r="O101" s="13">
+        <f>IF(N101="","",IF(N101&lt;=5000,"⚠値下げストップ","OK"))</f>
+        <v/>
+      </c>
+      <c r="P101" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
-  <dataValidations count="2">
+  <autoFilter ref="A1:P101"/>
+  <dataValidations count="3">
     <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"財布,バッグ"</formula1>
     </dataValidation>
     <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82 E83 E84 E85 E86 E87 E88 E89 E90 E91 E92 E93 E94 E95 E96 E97 E98 E99 E100 E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"エコリング,オークネット,ヤフオク,メルカリ"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"メルカリ,PayPay,ラクマ,ヤフオク,エコリング"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/管理スプレッドシート.xlsx
+++ b/管理スプレッドシート.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>想定手数料</t>
+          <t>想定手数料（自動）</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -635,7 +635,10 @@
       </c>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
+      <c r="L2" s="4">
+        <f>IF(OR(K2="",J2=""),"",IF(J2="PayPay",ROUND(K2*0.05),IF(J2="エコリング",0,ROUND(K2*0.1))))</f>
+        <v/>
+      </c>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4">
         <f>IF(K2="","",K2-G2-L2-M2)</f>
@@ -684,7 +687,10 @@
       </c>
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
+      <c r="L3" s="8">
+        <f>IF(OR(K3="",J3=""),"",IF(J3="PayPay",ROUND(K3*0.05),IF(J3="エコリング",0,ROUND(K3*0.1))))</f>
+        <v/>
+      </c>
       <c r="M3" s="8" t="n"/>
       <c r="N3" s="8">
         <f>IF(K3="","",K3-G3-L3-M3)</f>
@@ -737,7 +743,10 @@
       </c>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="L4" s="4">
+        <f>IF(OR(K4="",J4=""),"",IF(J4="PayPay",ROUND(K4*0.05),IF(J4="エコリング",0,ROUND(K4*0.1))))</f>
+        <v/>
+      </c>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4">
         <f>IF(K4="","",K4-G4-L4-M4)</f>
@@ -790,7 +799,10 @@
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
+      <c r="L5" s="8">
+        <f>IF(OR(K5="",J5=""),"",IF(J5="PayPay",ROUND(K5*0.05),IF(J5="エコリング",0,ROUND(K5*0.1))))</f>
+        <v/>
+      </c>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8">
         <f>IF(K5="","",K5-G5-L5-M5)</f>
@@ -839,7 +851,10 @@
       </c>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+      <c r="L6" s="4">
+        <f>IF(OR(K6="",J6=""),"",IF(J6="PayPay",ROUND(K6*0.05),IF(J6="エコリング",0,ROUND(K6*0.1))))</f>
+        <v/>
+      </c>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4">
         <f>IF(K6="","",K6-G6-L6-M6)</f>
@@ -888,7 +903,10 @@
       </c>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
+      <c r="L7" s="8">
+        <f>IF(OR(K7="",J7=""),"",IF(J7="PayPay",ROUND(K7*0.05),IF(J7="エコリング",0,ROUND(K7*0.1))))</f>
+        <v/>
+      </c>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8">
         <f>IF(K7="","",K7-G7-L7-M7)</f>
@@ -937,7 +955,10 @@
       </c>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="L8" s="4">
+        <f>IF(OR(K8="",J8=""),"",IF(J8="PayPay",ROUND(K8*0.05),IF(J8="エコリング",0,ROUND(K8*0.1))))</f>
+        <v/>
+      </c>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4">
         <f>IF(K8="","",K8-G8-L8-M8)</f>
@@ -986,7 +1007,10 @@
       </c>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
+      <c r="L9" s="8">
+        <f>IF(OR(K9="",J9=""),"",IF(J9="PayPay",ROUND(K9*0.05),IF(J9="エコリング",0,ROUND(K9*0.1))))</f>
+        <v/>
+      </c>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8">
         <f>IF(K9="","",K9-G9-L9-M9)</f>
@@ -1035,7 +1059,10 @@
       </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
+      <c r="L10" s="4">
+        <f>IF(OR(K10="",J10=""),"",IF(J10="PayPay",ROUND(K10*0.05),IF(J10="エコリング",0,ROUND(K10*0.1))))</f>
+        <v/>
+      </c>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4">
         <f>IF(K10="","",K10-G10-L10-M10)</f>
@@ -1088,7 +1115,10 @@
       </c>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
+      <c r="L11" s="8">
+        <f>IF(OR(K11="",J11=""),"",IF(J11="PayPay",ROUND(K11*0.05),IF(J11="エコリング",0,ROUND(K11*0.1))))</f>
+        <v/>
+      </c>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8">
         <f>IF(K11="","",K11-G11-L11-M11)</f>
@@ -1137,7 +1167,10 @@
       </c>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
+      <c r="L12" s="4">
+        <f>IF(OR(K12="",J12=""),"",IF(J12="PayPay",ROUND(K12*0.05),IF(J12="エコリング",0,ROUND(K12*0.1))))</f>
+        <v/>
+      </c>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4">
         <f>IF(K12="","",K12-G12-L12-M12)</f>
@@ -1186,7 +1219,10 @@
       </c>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
+      <c r="L13" s="8">
+        <f>IF(OR(K13="",J13=""),"",IF(J13="PayPay",ROUND(K13*0.05),IF(J13="エコリング",0,ROUND(K13*0.1))))</f>
+        <v/>
+      </c>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8">
         <f>IF(K13="","",K13-G13-L13-M13)</f>
@@ -1235,7 +1271,10 @@
       </c>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
+      <c r="L14" s="4">
+        <f>IF(OR(K14="",J14=""),"",IF(J14="PayPay",ROUND(K14*0.05),IF(J14="エコリング",0,ROUND(K14*0.1))))</f>
+        <v/>
+      </c>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4">
         <f>IF(K14="","",K14-G14-L14-M14)</f>
@@ -1288,7 +1327,10 @@
       </c>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
+      <c r="L15" s="8">
+        <f>IF(OR(K15="",J15=""),"",IF(J15="PayPay",ROUND(K15*0.05),IF(J15="エコリング",0,ROUND(K15*0.1))))</f>
+        <v/>
+      </c>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8">
         <f>IF(K15="","",K15-G15-L15-M15)</f>
@@ -1337,7 +1379,10 @@
       </c>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
+      <c r="L16" s="4">
+        <f>IF(OR(K16="",J16=""),"",IF(J16="PayPay",ROUND(K16*0.05),IF(J16="エコリング",0,ROUND(K16*0.1))))</f>
+        <v/>
+      </c>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4">
         <f>IF(K16="","",K16-G16-L16-M16)</f>
@@ -1386,7 +1431,10 @@
       </c>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
+      <c r="L17" s="8">
+        <f>IF(OR(K17="",J17=""),"",IF(J17="PayPay",ROUND(K17*0.05),IF(J17="エコリング",0,ROUND(K17*0.1))))</f>
+        <v/>
+      </c>
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8">
         <f>IF(K17="","",K17-G17-L17-M17)</f>
@@ -1435,7 +1483,10 @@
       </c>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
+      <c r="L18" s="4">
+        <f>IF(OR(K18="",J18=""),"",IF(J18="PayPay",ROUND(K18*0.05),IF(J18="エコリング",0,ROUND(K18*0.1))))</f>
+        <v/>
+      </c>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4">
         <f>IF(K18="","",K18-G18-L18-M18)</f>
@@ -1484,7 +1535,10 @@
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
+      <c r="L19" s="8">
+        <f>IF(OR(K19="",J19=""),"",IF(J19="PayPay",ROUND(K19*0.05),IF(J19="エコリング",0,ROUND(K19*0.1))))</f>
+        <v/>
+      </c>
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="8">
         <f>IF(K19="","",K19-G19-L19-M19)</f>
@@ -1511,7 +1565,10 @@
       </c>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
+      <c r="L20" s="4">
+        <f>IF(OR(K20="",J20=""),"",IF(J20="PayPay",ROUND(K20*0.05),IF(J20="エコリング",0,ROUND(K20*0.1))))</f>
+        <v/>
+      </c>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4">
         <f>IF(K20="","",K20-G20-L20-M20)</f>
@@ -1538,7 +1595,10 @@
       </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
+      <c r="L21" s="8">
+        <f>IF(OR(K21="",J21=""),"",IF(J21="PayPay",ROUND(K21*0.05),IF(J21="エコリング",0,ROUND(K21*0.1))))</f>
+        <v/>
+      </c>
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8">
         <f>IF(K21="","",K21-G21-L21-M21)</f>
@@ -1565,7 +1625,10 @@
       </c>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
+      <c r="L22" s="4">
+        <f>IF(OR(K22="",J22=""),"",IF(J22="PayPay",ROUND(K22*0.05),IF(J22="エコリング",0,ROUND(K22*0.1))))</f>
+        <v/>
+      </c>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4">
         <f>IF(K22="","",K22-G22-L22-M22)</f>
@@ -1592,7 +1655,10 @@
       </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
+      <c r="L23" s="8">
+        <f>IF(OR(K23="",J23=""),"",IF(J23="PayPay",ROUND(K23*0.05),IF(J23="エコリング",0,ROUND(K23*0.1))))</f>
+        <v/>
+      </c>
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8">
         <f>IF(K23="","",K23-G23-L23-M23)</f>
@@ -1619,7 +1685,10 @@
       </c>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
+      <c r="L24" s="4">
+        <f>IF(OR(K24="",J24=""),"",IF(J24="PayPay",ROUND(K24*0.05),IF(J24="エコリング",0,ROUND(K24*0.1))))</f>
+        <v/>
+      </c>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4">
         <f>IF(K24="","",K24-G24-L24-M24)</f>
@@ -1646,7 +1715,10 @@
       </c>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="8" t="n"/>
-      <c r="L25" s="8" t="n"/>
+      <c r="L25" s="8">
+        <f>IF(OR(K25="",J25=""),"",IF(J25="PayPay",ROUND(K25*0.05),IF(J25="エコリング",0,ROUND(K25*0.1))))</f>
+        <v/>
+      </c>
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8">
         <f>IF(K25="","",K25-G25-L25-M25)</f>
@@ -1673,7 +1745,10 @@
       </c>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
+      <c r="L26" s="4">
+        <f>IF(OR(K26="",J26=""),"",IF(J26="PayPay",ROUND(K26*0.05),IF(J26="エコリング",0,ROUND(K26*0.1))))</f>
+        <v/>
+      </c>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4">
         <f>IF(K26="","",K26-G26-L26-M26)</f>
@@ -1700,7 +1775,10 @@
       </c>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="8" t="n"/>
-      <c r="L27" s="8" t="n"/>
+      <c r="L27" s="8">
+        <f>IF(OR(K27="",J27=""),"",IF(J27="PayPay",ROUND(K27*0.05),IF(J27="エコリング",0,ROUND(K27*0.1))))</f>
+        <v/>
+      </c>
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8">
         <f>IF(K27="","",K27-G27-L27-M27)</f>
@@ -1727,7 +1805,10 @@
       </c>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
+      <c r="L28" s="4">
+        <f>IF(OR(K28="",J28=""),"",IF(J28="PayPay",ROUND(K28*0.05),IF(J28="エコリング",0,ROUND(K28*0.1))))</f>
+        <v/>
+      </c>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4">
         <f>IF(K28="","",K28-G28-L28-M28)</f>
@@ -1754,7 +1835,10 @@
       </c>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="8" t="n"/>
-      <c r="L29" s="8" t="n"/>
+      <c r="L29" s="8">
+        <f>IF(OR(K29="",J29=""),"",IF(J29="PayPay",ROUND(K29*0.05),IF(J29="エコリング",0,ROUND(K29*0.1))))</f>
+        <v/>
+      </c>
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8">
         <f>IF(K29="","",K29-G29-L29-M29)</f>
@@ -1781,7 +1865,10 @@
       </c>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
+      <c r="L30" s="4">
+        <f>IF(OR(K30="",J30=""),"",IF(J30="PayPay",ROUND(K30*0.05),IF(J30="エコリング",0,ROUND(K30*0.1))))</f>
+        <v/>
+      </c>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4">
         <f>IF(K30="","",K30-G30-L30-M30)</f>
@@ -1808,7 +1895,10 @@
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="8" t="n"/>
-      <c r="L31" s="8" t="n"/>
+      <c r="L31" s="8">
+        <f>IF(OR(K31="",J31=""),"",IF(J31="PayPay",ROUND(K31*0.05),IF(J31="エコリング",0,ROUND(K31*0.1))))</f>
+        <v/>
+      </c>
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8">
         <f>IF(K31="","",K31-G31-L31-M31)</f>
@@ -1835,7 +1925,10 @@
       </c>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
+      <c r="L32" s="4">
+        <f>IF(OR(K32="",J32=""),"",IF(J32="PayPay",ROUND(K32*0.05),IF(J32="エコリング",0,ROUND(K32*0.1))))</f>
+        <v/>
+      </c>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4">
         <f>IF(K32="","",K32-G32-L32-M32)</f>
@@ -1862,7 +1955,10 @@
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="8" t="n"/>
-      <c r="L33" s="8" t="n"/>
+      <c r="L33" s="8">
+        <f>IF(OR(K33="",J33=""),"",IF(J33="PayPay",ROUND(K33*0.05),IF(J33="エコリング",0,ROUND(K33*0.1))))</f>
+        <v/>
+      </c>
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8">
         <f>IF(K33="","",K33-G33-L33-M33)</f>
@@ -1889,7 +1985,10 @@
       </c>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
+      <c r="L34" s="4">
+        <f>IF(OR(K34="",J34=""),"",IF(J34="PayPay",ROUND(K34*0.05),IF(J34="エコリング",0,ROUND(K34*0.1))))</f>
+        <v/>
+      </c>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4">
         <f>IF(K34="","",K34-G34-L34-M34)</f>
@@ -1916,7 +2015,10 @@
       </c>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="8" t="n"/>
-      <c r="L35" s="8" t="n"/>
+      <c r="L35" s="8">
+        <f>IF(OR(K35="",J35=""),"",IF(J35="PayPay",ROUND(K35*0.05),IF(J35="エコリング",0,ROUND(K35*0.1))))</f>
+        <v/>
+      </c>
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8">
         <f>IF(K35="","",K35-G35-L35-M35)</f>
@@ -1943,7 +2045,10 @@
       </c>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
+      <c r="L36" s="4">
+        <f>IF(OR(K36="",J36=""),"",IF(J36="PayPay",ROUND(K36*0.05),IF(J36="エコリング",0,ROUND(K36*0.1))))</f>
+        <v/>
+      </c>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4">
         <f>IF(K36="","",K36-G36-L36-M36)</f>
@@ -1970,7 +2075,10 @@
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="8" t="n"/>
-      <c r="L37" s="8" t="n"/>
+      <c r="L37" s="8">
+        <f>IF(OR(K37="",J37=""),"",IF(J37="PayPay",ROUND(K37*0.05),IF(J37="エコリング",0,ROUND(K37*0.1))))</f>
+        <v/>
+      </c>
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8">
         <f>IF(K37="","",K37-G37-L37-M37)</f>
@@ -1997,7 +2105,10 @@
       </c>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
+      <c r="L38" s="4">
+        <f>IF(OR(K38="",J38=""),"",IF(J38="PayPay",ROUND(K38*0.05),IF(J38="エコリング",0,ROUND(K38*0.1))))</f>
+        <v/>
+      </c>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4">
         <f>IF(K38="","",K38-G38-L38-M38)</f>
@@ -2024,7 +2135,10 @@
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="8" t="n"/>
-      <c r="L39" s="8" t="n"/>
+      <c r="L39" s="8">
+        <f>IF(OR(K39="",J39=""),"",IF(J39="PayPay",ROUND(K39*0.05),IF(J39="エコリング",0,ROUND(K39*0.1))))</f>
+        <v/>
+      </c>
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8">
         <f>IF(K39="","",K39-G39-L39-M39)</f>
@@ -2051,7 +2165,10 @@
       </c>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
+      <c r="L40" s="4">
+        <f>IF(OR(K40="",J40=""),"",IF(J40="PayPay",ROUND(K40*0.05),IF(J40="エコリング",0,ROUND(K40*0.1))))</f>
+        <v/>
+      </c>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4">
         <f>IF(K40="","",K40-G40-L40-M40)</f>
@@ -2078,7 +2195,10 @@
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="8" t="n"/>
-      <c r="L41" s="8" t="n"/>
+      <c r="L41" s="8">
+        <f>IF(OR(K41="",J41=""),"",IF(J41="PayPay",ROUND(K41*0.05),IF(J41="エコリング",0,ROUND(K41*0.1))))</f>
+        <v/>
+      </c>
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8">
         <f>IF(K41="","",K41-G41-L41-M41)</f>
@@ -2105,7 +2225,10 @@
       </c>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n"/>
+      <c r="L42" s="4">
+        <f>IF(OR(K42="",J42=""),"",IF(J42="PayPay",ROUND(K42*0.05),IF(J42="エコリング",0,ROUND(K42*0.1))))</f>
+        <v/>
+      </c>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4">
         <f>IF(K42="","",K42-G42-L42-M42)</f>
@@ -2132,7 +2255,10 @@
       </c>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="8" t="n"/>
-      <c r="L43" s="8" t="n"/>
+      <c r="L43" s="8">
+        <f>IF(OR(K43="",J43=""),"",IF(J43="PayPay",ROUND(K43*0.05),IF(J43="エコリング",0,ROUND(K43*0.1))))</f>
+        <v/>
+      </c>
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8">
         <f>IF(K43="","",K43-G43-L43-M43)</f>
@@ -2159,7 +2285,10 @@
       </c>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
+      <c r="L44" s="4">
+        <f>IF(OR(K44="",J44=""),"",IF(J44="PayPay",ROUND(K44*0.05),IF(J44="エコリング",0,ROUND(K44*0.1))))</f>
+        <v/>
+      </c>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4">
         <f>IF(K44="","",K44-G44-L44-M44)</f>
@@ -2186,7 +2315,10 @@
       </c>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="8" t="n"/>
-      <c r="L45" s="8" t="n"/>
+      <c r="L45" s="8">
+        <f>IF(OR(K45="",J45=""),"",IF(J45="PayPay",ROUND(K45*0.05),IF(J45="エコリング",0,ROUND(K45*0.1))))</f>
+        <v/>
+      </c>
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8">
         <f>IF(K45="","",K45-G45-L45-M45)</f>
@@ -2213,7 +2345,10 @@
       </c>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
+      <c r="L46" s="4">
+        <f>IF(OR(K46="",J46=""),"",IF(J46="PayPay",ROUND(K46*0.05),IF(J46="エコリング",0,ROUND(K46*0.1))))</f>
+        <v/>
+      </c>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4">
         <f>IF(K46="","",K46-G46-L46-M46)</f>
@@ -2240,7 +2375,10 @@
       </c>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="8" t="n"/>
-      <c r="L47" s="8" t="n"/>
+      <c r="L47" s="8">
+        <f>IF(OR(K47="",J47=""),"",IF(J47="PayPay",ROUND(K47*0.05),IF(J47="エコリング",0,ROUND(K47*0.1))))</f>
+        <v/>
+      </c>
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8">
         <f>IF(K47="","",K47-G47-L47-M47)</f>
@@ -2267,7 +2405,10 @@
       </c>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
+      <c r="L48" s="4">
+        <f>IF(OR(K48="",J48=""),"",IF(J48="PayPay",ROUND(K48*0.05),IF(J48="エコリング",0,ROUND(K48*0.1))))</f>
+        <v/>
+      </c>
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4">
         <f>IF(K48="","",K48-G48-L48-M48)</f>
@@ -2294,7 +2435,10 @@
       </c>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="8" t="n"/>
-      <c r="L49" s="8" t="n"/>
+      <c r="L49" s="8">
+        <f>IF(OR(K49="",J49=""),"",IF(J49="PayPay",ROUND(K49*0.05),IF(J49="エコリング",0,ROUND(K49*0.1))))</f>
+        <v/>
+      </c>
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8">
         <f>IF(K49="","",K49-G49-L49-M49)</f>
@@ -2321,7 +2465,10 @@
       </c>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="4" t="n"/>
-      <c r="L50" s="4" t="n"/>
+      <c r="L50" s="4">
+        <f>IF(OR(K50="",J50=""),"",IF(J50="PayPay",ROUND(K50*0.05),IF(J50="エコリング",0,ROUND(K50*0.1))))</f>
+        <v/>
+      </c>
       <c r="M50" s="4" t="n"/>
       <c r="N50" s="4">
         <f>IF(K50="","",K50-G50-L50-M50)</f>
@@ -2348,7 +2495,10 @@
       </c>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="8" t="n"/>
-      <c r="L51" s="8" t="n"/>
+      <c r="L51" s="8">
+        <f>IF(OR(K51="",J51=""),"",IF(J51="PayPay",ROUND(K51*0.05),IF(J51="エコリング",0,ROUND(K51*0.1))))</f>
+        <v/>
+      </c>
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8">
         <f>IF(K51="","",K51-G51-L51-M51)</f>
@@ -2375,7 +2525,10 @@
       </c>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
+      <c r="L52" s="4">
+        <f>IF(OR(K52="",J52=""),"",IF(J52="PayPay",ROUND(K52*0.05),IF(J52="エコリング",0,ROUND(K52*0.1))))</f>
+        <v/>
+      </c>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4">
         <f>IF(K52="","",K52-G52-L52-M52)</f>
@@ -2402,7 +2555,10 @@
       </c>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="8" t="n"/>
-      <c r="L53" s="8" t="n"/>
+      <c r="L53" s="8">
+        <f>IF(OR(K53="",J53=""),"",IF(J53="PayPay",ROUND(K53*0.05),IF(J53="エコリング",0,ROUND(K53*0.1))))</f>
+        <v/>
+      </c>
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8">
         <f>IF(K53="","",K53-G53-L53-M53)</f>
@@ -2429,7 +2585,10 @@
       </c>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
+      <c r="L54" s="4">
+        <f>IF(OR(K54="",J54=""),"",IF(J54="PayPay",ROUND(K54*0.05),IF(J54="エコリング",0,ROUND(K54*0.1))))</f>
+        <v/>
+      </c>
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4">
         <f>IF(K54="","",K54-G54-L54-M54)</f>
@@ -2456,7 +2615,10 @@
       </c>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="8" t="n"/>
-      <c r="L55" s="8" t="n"/>
+      <c r="L55" s="8">
+        <f>IF(OR(K55="",J55=""),"",IF(J55="PayPay",ROUND(K55*0.05),IF(J55="エコリング",0,ROUND(K55*0.1))))</f>
+        <v/>
+      </c>
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8">
         <f>IF(K55="","",K55-G55-L55-M55)</f>
@@ -2483,7 +2645,10 @@
       </c>
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="4" t="n"/>
-      <c r="L56" s="4" t="n"/>
+      <c r="L56" s="4">
+        <f>IF(OR(K56="",J56=""),"",IF(J56="PayPay",ROUND(K56*0.05),IF(J56="エコリング",0,ROUND(K56*0.1))))</f>
+        <v/>
+      </c>
       <c r="M56" s="4" t="n"/>
       <c r="N56" s="4">
         <f>IF(K56="","",K56-G56-L56-M56)</f>
@@ -2510,7 +2675,10 @@
       </c>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="8" t="n"/>
-      <c r="L57" s="8" t="n"/>
+      <c r="L57" s="8">
+        <f>IF(OR(K57="",J57=""),"",IF(J57="PayPay",ROUND(K57*0.05),IF(J57="エコリング",0,ROUND(K57*0.1))))</f>
+        <v/>
+      </c>
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8">
         <f>IF(K57="","",K57-G57-L57-M57)</f>
@@ -2537,7 +2705,10 @@
       </c>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="4" t="n"/>
-      <c r="L58" s="4" t="n"/>
+      <c r="L58" s="4">
+        <f>IF(OR(K58="",J58=""),"",IF(J58="PayPay",ROUND(K58*0.05),IF(J58="エコリング",0,ROUND(K58*0.1))))</f>
+        <v/>
+      </c>
       <c r="M58" s="4" t="n"/>
       <c r="N58" s="4">
         <f>IF(K58="","",K58-G58-L58-M58)</f>
@@ -2564,7 +2735,10 @@
       </c>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="8" t="n"/>
-      <c r="L59" s="8" t="n"/>
+      <c r="L59" s="8">
+        <f>IF(OR(K59="",J59=""),"",IF(J59="PayPay",ROUND(K59*0.05),IF(J59="エコリング",0,ROUND(K59*0.1))))</f>
+        <v/>
+      </c>
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8">
         <f>IF(K59="","",K59-G59-L59-M59)</f>
@@ -2591,7 +2765,10 @@
       </c>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
+      <c r="L60" s="4">
+        <f>IF(OR(K60="",J60=""),"",IF(J60="PayPay",ROUND(K60*0.05),IF(J60="エコリング",0,ROUND(K60*0.1))))</f>
+        <v/>
+      </c>
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4">
         <f>IF(K60="","",K60-G60-L60-M60)</f>
@@ -2618,7 +2795,10 @@
       </c>
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="8" t="n"/>
-      <c r="L61" s="8" t="n"/>
+      <c r="L61" s="8">
+        <f>IF(OR(K61="",J61=""),"",IF(J61="PayPay",ROUND(K61*0.05),IF(J61="エコリング",0,ROUND(K61*0.1))))</f>
+        <v/>
+      </c>
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8">
         <f>IF(K61="","",K61-G61-L61-M61)</f>
@@ -2645,7 +2825,10 @@
       </c>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n"/>
+      <c r="L62" s="4">
+        <f>IF(OR(K62="",J62=""),"",IF(J62="PayPay",ROUND(K62*0.05),IF(J62="エコリング",0,ROUND(K62*0.1))))</f>
+        <v/>
+      </c>
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4">
         <f>IF(K62="","",K62-G62-L62-M62)</f>
@@ -2672,7 +2855,10 @@
       </c>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="8" t="n"/>
-      <c r="L63" s="8" t="n"/>
+      <c r="L63" s="8">
+        <f>IF(OR(K63="",J63=""),"",IF(J63="PayPay",ROUND(K63*0.05),IF(J63="エコリング",0,ROUND(K63*0.1))))</f>
+        <v/>
+      </c>
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8">
         <f>IF(K63="","",K63-G63-L63-M63)</f>
@@ -2699,7 +2885,10 @@
       </c>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
+      <c r="L64" s="4">
+        <f>IF(OR(K64="",J64=""),"",IF(J64="PayPay",ROUND(K64*0.05),IF(J64="エコリング",0,ROUND(K64*0.1))))</f>
+        <v/>
+      </c>
       <c r="M64" s="4" t="n"/>
       <c r="N64" s="4">
         <f>IF(K64="","",K64-G64-L64-M64)</f>
@@ -2726,7 +2915,10 @@
       </c>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="8" t="n"/>
-      <c r="L65" s="8" t="n"/>
+      <c r="L65" s="8">
+        <f>IF(OR(K65="",J65=""),"",IF(J65="PayPay",ROUND(K65*0.05),IF(J65="エコリング",0,ROUND(K65*0.1))))</f>
+        <v/>
+      </c>
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8">
         <f>IF(K65="","",K65-G65-L65-M65)</f>
@@ -2753,7 +2945,10 @@
       </c>
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
+      <c r="L66" s="4">
+        <f>IF(OR(K66="",J66=""),"",IF(J66="PayPay",ROUND(K66*0.05),IF(J66="エコリング",0,ROUND(K66*0.1))))</f>
+        <v/>
+      </c>
       <c r="M66" s="4" t="n"/>
       <c r="N66" s="4">
         <f>IF(K66="","",K66-G66-L66-M66)</f>
@@ -2780,7 +2975,10 @@
       </c>
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="8" t="n"/>
-      <c r="L67" s="8" t="n"/>
+      <c r="L67" s="8">
+        <f>IF(OR(K67="",J67=""),"",IF(J67="PayPay",ROUND(K67*0.05),IF(J67="エコリング",0,ROUND(K67*0.1))))</f>
+        <v/>
+      </c>
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8">
         <f>IF(K67="","",K67-G67-L67-M67)</f>
@@ -2807,7 +3005,10 @@
       </c>
       <c r="J68" s="2" t="n"/>
       <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
+      <c r="L68" s="4">
+        <f>IF(OR(K68="",J68=""),"",IF(J68="PayPay",ROUND(K68*0.05),IF(J68="エコリング",0,ROUND(K68*0.1))))</f>
+        <v/>
+      </c>
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4">
         <f>IF(K68="","",K68-G68-L68-M68)</f>
@@ -2834,7 +3035,10 @@
       </c>
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
+      <c r="L69" s="8">
+        <f>IF(OR(K69="",J69=""),"",IF(J69="PayPay",ROUND(K69*0.05),IF(J69="エコリング",0,ROUND(K69*0.1))))</f>
+        <v/>
+      </c>
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8">
         <f>IF(K69="","",K69-G69-L69-M69)</f>
@@ -2861,7 +3065,10 @@
       </c>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="n"/>
+      <c r="L70" s="4">
+        <f>IF(OR(K70="",J70=""),"",IF(J70="PayPay",ROUND(K70*0.05),IF(J70="エコリング",0,ROUND(K70*0.1))))</f>
+        <v/>
+      </c>
       <c r="M70" s="4" t="n"/>
       <c r="N70" s="4">
         <f>IF(K70="","",K70-G70-L70-M70)</f>
@@ -2888,7 +3095,10 @@
       </c>
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="8" t="n"/>
-      <c r="L71" s="8" t="n"/>
+      <c r="L71" s="8">
+        <f>IF(OR(K71="",J71=""),"",IF(J71="PayPay",ROUND(K71*0.05),IF(J71="エコリング",0,ROUND(K71*0.1))))</f>
+        <v/>
+      </c>
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8">
         <f>IF(K71="","",K71-G71-L71-M71)</f>
@@ -2915,7 +3125,10 @@
       </c>
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
+      <c r="L72" s="4">
+        <f>IF(OR(K72="",J72=""),"",IF(J72="PayPay",ROUND(K72*0.05),IF(J72="エコリング",0,ROUND(K72*0.1))))</f>
+        <v/>
+      </c>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4">
         <f>IF(K72="","",K72-G72-L72-M72)</f>
@@ -2942,7 +3155,10 @@
       </c>
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="8" t="n"/>
-      <c r="L73" s="8" t="n"/>
+      <c r="L73" s="8">
+        <f>IF(OR(K73="",J73=""),"",IF(J73="PayPay",ROUND(K73*0.05),IF(J73="エコリング",0,ROUND(K73*0.1))))</f>
+        <v/>
+      </c>
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8">
         <f>IF(K73="","",K73-G73-L73-M73)</f>
@@ -2969,7 +3185,10 @@
       </c>
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
+      <c r="L74" s="4">
+        <f>IF(OR(K74="",J74=""),"",IF(J74="PayPay",ROUND(K74*0.05),IF(J74="エコリング",0,ROUND(K74*0.1))))</f>
+        <v/>
+      </c>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4">
         <f>IF(K74="","",K74-G74-L74-M74)</f>
@@ -2996,7 +3215,10 @@
       </c>
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="8" t="n"/>
-      <c r="L75" s="8" t="n"/>
+      <c r="L75" s="8">
+        <f>IF(OR(K75="",J75=""),"",IF(J75="PayPay",ROUND(K75*0.05),IF(J75="エコリング",0,ROUND(K75*0.1))))</f>
+        <v/>
+      </c>
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="8">
         <f>IF(K75="","",K75-G75-L75-M75)</f>
@@ -3023,7 +3245,10 @@
       </c>
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="n"/>
+      <c r="L76" s="4">
+        <f>IF(OR(K76="",J76=""),"",IF(J76="PayPay",ROUND(K76*0.05),IF(J76="エコリング",0,ROUND(K76*0.1))))</f>
+        <v/>
+      </c>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4">
         <f>IF(K76="","",K76-G76-L76-M76)</f>
@@ -3050,7 +3275,10 @@
       </c>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="8" t="n"/>
-      <c r="L77" s="8" t="n"/>
+      <c r="L77" s="8">
+        <f>IF(OR(K77="",J77=""),"",IF(J77="PayPay",ROUND(K77*0.05),IF(J77="エコリング",0,ROUND(K77*0.1))))</f>
+        <v/>
+      </c>
       <c r="M77" s="8" t="n"/>
       <c r="N77" s="8">
         <f>IF(K77="","",K77-G77-L77-M77)</f>
@@ -3077,7 +3305,10 @@
       </c>
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="4" t="n"/>
-      <c r="L78" s="4" t="n"/>
+      <c r="L78" s="4">
+        <f>IF(OR(K78="",J78=""),"",IF(J78="PayPay",ROUND(K78*0.05),IF(J78="エコリング",0,ROUND(K78*0.1))))</f>
+        <v/>
+      </c>
       <c r="M78" s="4" t="n"/>
       <c r="N78" s="4">
         <f>IF(K78="","",K78-G78-L78-M78)</f>
@@ -3104,7 +3335,10 @@
       </c>
       <c r="J79" s="6" t="n"/>
       <c r="K79" s="8" t="n"/>
-      <c r="L79" s="8" t="n"/>
+      <c r="L79" s="8">
+        <f>IF(OR(K79="",J79=""),"",IF(J79="PayPay",ROUND(K79*0.05),IF(J79="エコリング",0,ROUND(K79*0.1))))</f>
+        <v/>
+      </c>
       <c r="M79" s="8" t="n"/>
       <c r="N79" s="8">
         <f>IF(K79="","",K79-G79-L79-M79)</f>
@@ -3131,7 +3365,10 @@
       </c>
       <c r="J80" s="2" t="n"/>
       <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n"/>
+      <c r="L80" s="4">
+        <f>IF(OR(K80="",J80=""),"",IF(J80="PayPay",ROUND(K80*0.05),IF(J80="エコリング",0,ROUND(K80*0.1))))</f>
+        <v/>
+      </c>
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4">
         <f>IF(K80="","",K80-G80-L80-M80)</f>
@@ -3158,7 +3395,10 @@
       </c>
       <c r="J81" s="6" t="n"/>
       <c r="K81" s="8" t="n"/>
-      <c r="L81" s="8" t="n"/>
+      <c r="L81" s="8">
+        <f>IF(OR(K81="",J81=""),"",IF(J81="PayPay",ROUND(K81*0.05),IF(J81="エコリング",0,ROUND(K81*0.1))))</f>
+        <v/>
+      </c>
       <c r="M81" s="8" t="n"/>
       <c r="N81" s="8">
         <f>IF(K81="","",K81-G81-L81-M81)</f>
@@ -3185,7 +3425,10 @@
       </c>
       <c r="J82" s="2" t="n"/>
       <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
+      <c r="L82" s="4">
+        <f>IF(OR(K82="",J82=""),"",IF(J82="PayPay",ROUND(K82*0.05),IF(J82="エコリング",0,ROUND(K82*0.1))))</f>
+        <v/>
+      </c>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4">
         <f>IF(K82="","",K82-G82-L82-M82)</f>
@@ -3212,7 +3455,10 @@
       </c>
       <c r="J83" s="6" t="n"/>
       <c r="K83" s="8" t="n"/>
-      <c r="L83" s="8" t="n"/>
+      <c r="L83" s="8">
+        <f>IF(OR(K83="",J83=""),"",IF(J83="PayPay",ROUND(K83*0.05),IF(J83="エコリング",0,ROUND(K83*0.1))))</f>
+        <v/>
+      </c>
       <c r="M83" s="8" t="n"/>
       <c r="N83" s="8">
         <f>IF(K83="","",K83-G83-L83-M83)</f>
@@ -3239,7 +3485,10 @@
       </c>
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n"/>
+      <c r="L84" s="4">
+        <f>IF(OR(K84="",J84=""),"",IF(J84="PayPay",ROUND(K84*0.05),IF(J84="エコリング",0,ROUND(K84*0.1))))</f>
+        <v/>
+      </c>
       <c r="M84" s="4" t="n"/>
       <c r="N84" s="4">
         <f>IF(K84="","",K84-G84-L84-M84)</f>
@@ -3266,7 +3515,10 @@
       </c>
       <c r="J85" s="6" t="n"/>
       <c r="K85" s="8" t="n"/>
-      <c r="L85" s="8" t="n"/>
+      <c r="L85" s="8">
+        <f>IF(OR(K85="",J85=""),"",IF(J85="PayPay",ROUND(K85*0.05),IF(J85="エコリング",0,ROUND(K85*0.1))))</f>
+        <v/>
+      </c>
       <c r="M85" s="8" t="n"/>
       <c r="N85" s="8">
         <f>IF(K85="","",K85-G85-L85-M85)</f>
@@ -3293,7 +3545,10 @@
       </c>
       <c r="J86" s="2" t="n"/>
       <c r="K86" s="4" t="n"/>
-      <c r="L86" s="4" t="n"/>
+      <c r="L86" s="4">
+        <f>IF(OR(K86="",J86=""),"",IF(J86="PayPay",ROUND(K86*0.05),IF(J86="エコリング",0,ROUND(K86*0.1))))</f>
+        <v/>
+      </c>
       <c r="M86" s="4" t="n"/>
       <c r="N86" s="4">
         <f>IF(K86="","",K86-G86-L86-M86)</f>
@@ -3320,7 +3575,10 @@
       </c>
       <c r="J87" s="6" t="n"/>
       <c r="K87" s="8" t="n"/>
-      <c r="L87" s="8" t="n"/>
+      <c r="L87" s="8">
+        <f>IF(OR(K87="",J87=""),"",IF(J87="PayPay",ROUND(K87*0.05),IF(J87="エコリング",0,ROUND(K87*0.1))))</f>
+        <v/>
+      </c>
       <c r="M87" s="8" t="n"/>
       <c r="N87" s="8">
         <f>IF(K87="","",K87-G87-L87-M87)</f>
@@ -3347,7 +3605,10 @@
       </c>
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
+      <c r="L88" s="4">
+        <f>IF(OR(K88="",J88=""),"",IF(J88="PayPay",ROUND(K88*0.05),IF(J88="エコリング",0,ROUND(K88*0.1))))</f>
+        <v/>
+      </c>
       <c r="M88" s="4" t="n"/>
       <c r="N88" s="4">
         <f>IF(K88="","",K88-G88-L88-M88)</f>
@@ -3374,7 +3635,10 @@
       </c>
       <c r="J89" s="6" t="n"/>
       <c r="K89" s="8" t="n"/>
-      <c r="L89" s="8" t="n"/>
+      <c r="L89" s="8">
+        <f>IF(OR(K89="",J89=""),"",IF(J89="PayPay",ROUND(K89*0.05),IF(J89="エコリング",0,ROUND(K89*0.1))))</f>
+        <v/>
+      </c>
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="8">
         <f>IF(K89="","",K89-G89-L89-M89)</f>
@@ -3401,7 +3665,10 @@
       </c>
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="4" t="n"/>
-      <c r="L90" s="4" t="n"/>
+      <c r="L90" s="4">
+        <f>IF(OR(K90="",J90=""),"",IF(J90="PayPay",ROUND(K90*0.05),IF(J90="エコリング",0,ROUND(K90*0.1))))</f>
+        <v/>
+      </c>
       <c r="M90" s="4" t="n"/>
       <c r="N90" s="4">
         <f>IF(K90="","",K90-G90-L90-M90)</f>
@@ -3428,7 +3695,10 @@
       </c>
       <c r="J91" s="6" t="n"/>
       <c r="K91" s="8" t="n"/>
-      <c r="L91" s="8" t="n"/>
+      <c r="L91" s="8">
+        <f>IF(OR(K91="",J91=""),"",IF(J91="PayPay",ROUND(K91*0.05),IF(J91="エコリング",0,ROUND(K91*0.1))))</f>
+        <v/>
+      </c>
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8">
         <f>IF(K91="","",K91-G91-L91-M91)</f>
@@ -3455,7 +3725,10 @@
       </c>
       <c r="J92" s="2" t="n"/>
       <c r="K92" s="4" t="n"/>
-      <c r="L92" s="4" t="n"/>
+      <c r="L92" s="4">
+        <f>IF(OR(K92="",J92=""),"",IF(J92="PayPay",ROUND(K92*0.05),IF(J92="エコリング",0,ROUND(K92*0.1))))</f>
+        <v/>
+      </c>
       <c r="M92" s="4" t="n"/>
       <c r="N92" s="4">
         <f>IF(K92="","",K92-G92-L92-M92)</f>
@@ -3482,7 +3755,10 @@
       </c>
       <c r="J93" s="6" t="n"/>
       <c r="K93" s="8" t="n"/>
-      <c r="L93" s="8" t="n"/>
+      <c r="L93" s="8">
+        <f>IF(OR(K93="",J93=""),"",IF(J93="PayPay",ROUND(K93*0.05),IF(J93="エコリング",0,ROUND(K93*0.1))))</f>
+        <v/>
+      </c>
       <c r="M93" s="8" t="n"/>
       <c r="N93" s="8">
         <f>IF(K93="","",K93-G93-L93-M93)</f>
@@ -3509,7 +3785,10 @@
       </c>
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="4" t="n"/>
-      <c r="L94" s="4" t="n"/>
+      <c r="L94" s="4">
+        <f>IF(OR(K94="",J94=""),"",IF(J94="PayPay",ROUND(K94*0.05),IF(J94="エコリング",0,ROUND(K94*0.1))))</f>
+        <v/>
+      </c>
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4">
         <f>IF(K94="","",K94-G94-L94-M94)</f>
@@ -3536,7 +3815,10 @@
       </c>
       <c r="J95" s="6" t="n"/>
       <c r="K95" s="8" t="n"/>
-      <c r="L95" s="8" t="n"/>
+      <c r="L95" s="8">
+        <f>IF(OR(K95="",J95=""),"",IF(J95="PayPay",ROUND(K95*0.05),IF(J95="エコリング",0,ROUND(K95*0.1))))</f>
+        <v/>
+      </c>
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="8">
         <f>IF(K95="","",K95-G95-L95-M95)</f>
@@ -3563,7 +3845,10 @@
       </c>
       <c r="J96" s="2" t="n"/>
       <c r="K96" s="4" t="n"/>
-      <c r="L96" s="4" t="n"/>
+      <c r="L96" s="4">
+        <f>IF(OR(K96="",J96=""),"",IF(J96="PayPay",ROUND(K96*0.05),IF(J96="エコリング",0,ROUND(K96*0.1))))</f>
+        <v/>
+      </c>
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4">
         <f>IF(K96="","",K96-G96-L96-M96)</f>
@@ -3590,7 +3875,10 @@
       </c>
       <c r="J97" s="6" t="n"/>
       <c r="K97" s="8" t="n"/>
-      <c r="L97" s="8" t="n"/>
+      <c r="L97" s="8">
+        <f>IF(OR(K97="",J97=""),"",IF(J97="PayPay",ROUND(K97*0.05),IF(J97="エコリング",0,ROUND(K97*0.1))))</f>
+        <v/>
+      </c>
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8">
         <f>IF(K97="","",K97-G97-L97-M97)</f>
@@ -3617,7 +3905,10 @@
       </c>
       <c r="J98" s="2" t="n"/>
       <c r="K98" s="4" t="n"/>
-      <c r="L98" s="4" t="n"/>
+      <c r="L98" s="4">
+        <f>IF(OR(K98="",J98=""),"",IF(J98="PayPay",ROUND(K98*0.05),IF(J98="エコリング",0,ROUND(K98*0.1))))</f>
+        <v/>
+      </c>
       <c r="M98" s="4" t="n"/>
       <c r="N98" s="4">
         <f>IF(K98="","",K98-G98-L98-M98)</f>
@@ -3644,7 +3935,10 @@
       </c>
       <c r="J99" s="6" t="n"/>
       <c r="K99" s="8" t="n"/>
-      <c r="L99" s="8" t="n"/>
+      <c r="L99" s="8">
+        <f>IF(OR(K99="",J99=""),"",IF(J99="PayPay",ROUND(K99*0.05),IF(J99="エコリング",0,ROUND(K99*0.1))))</f>
+        <v/>
+      </c>
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8">
         <f>IF(K99="","",K99-G99-L99-M99)</f>
@@ -3671,7 +3965,10 @@
       </c>
       <c r="J100" s="2" t="n"/>
       <c r="K100" s="4" t="n"/>
-      <c r="L100" s="4" t="n"/>
+      <c r="L100" s="4">
+        <f>IF(OR(K100="",J100=""),"",IF(J100="PayPay",ROUND(K100*0.05),IF(J100="エコリング",0,ROUND(K100*0.1))))</f>
+        <v/>
+      </c>
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4">
         <f>IF(K100="","",K100-G100-L100-M100)</f>
@@ -3698,7 +3995,10 @@
       </c>
       <c r="J101" s="6" t="n"/>
       <c r="K101" s="8" t="n"/>
-      <c r="L101" s="8" t="n"/>
+      <c r="L101" s="8">
+        <f>IF(OR(K101="",J101=""),"",IF(J101="PayPay",ROUND(K101*0.05),IF(J101="エコリング",0,ROUND(K101*0.1))))</f>
+        <v/>
+      </c>
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8">
         <f>IF(K101="","",K101-G101-L101-M101)</f>
@@ -3712,7 +4012,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P101"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="C2 C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"財布,バッグ"</formula1>
     </dataValidation>
@@ -3721,6 +4021,9 @@
     </dataValidation>
     <dataValidation sqref="J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"メルカリ,PayPay,ラクマ,ヤフオク,エコリング"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2 M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 M71 M72 M73 M74 M75 M76 M77 M78 M79 M80 M81 M82 M83 M84 M85 M86 M87 M88 M89 M90 M91 M92 M93 M94 M95 M96 M97 M98 M99 M100 M101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"450,490,210"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/管理スプレッドシート.xlsx
+++ b/管理スプレッドシート.xlsx
@@ -636,7 +636,7 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4">
-        <f>IF(OR(K2="",J2=""),"",IF(J2="PayPay",ROUND(K2*0.05),IF(J2="エコリング",0,ROUND(K2*0.1))))</f>
+        <f>IF(OR(K2="",J2=""),"",IF(J2="エコリング","",IF(J2="PayPay",ROUND(K2*0.05),ROUND(K2*0.1))))</f>
         <v/>
       </c>
       <c r="M2" s="4" t="n"/>
@@ -688,7 +688,7 @@
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="8" t="n"/>
       <c r="L3" s="8">
-        <f>IF(OR(K3="",J3=""),"",IF(J3="PayPay",ROUND(K3*0.05),IF(J3="エコリング",0,ROUND(K3*0.1))))</f>
+        <f>IF(OR(K3="",J3=""),"",IF(J3="エコリング","",IF(J3="PayPay",ROUND(K3*0.05),ROUND(K3*0.1))))</f>
         <v/>
       </c>
       <c r="M3" s="8" t="n"/>
@@ -744,7 +744,7 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4">
-        <f>IF(OR(K4="",J4=""),"",IF(J4="PayPay",ROUND(K4*0.05),IF(J4="エコリング",0,ROUND(K4*0.1))))</f>
+        <f>IF(OR(K4="",J4=""),"",IF(J4="エコリング","",IF(J4="PayPay",ROUND(K4*0.05),ROUND(K4*0.1))))</f>
         <v/>
       </c>
       <c r="M4" s="4" t="n"/>
@@ -800,7 +800,7 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="8" t="n"/>
       <c r="L5" s="8">
-        <f>IF(OR(K5="",J5=""),"",IF(J5="PayPay",ROUND(K5*0.05),IF(J5="エコリング",0,ROUND(K5*0.1))))</f>
+        <f>IF(OR(K5="",J5=""),"",IF(J5="エコリング","",IF(J5="PayPay",ROUND(K5*0.05),ROUND(K5*0.1))))</f>
         <v/>
       </c>
       <c r="M5" s="8" t="n"/>
@@ -852,7 +852,7 @@
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4">
-        <f>IF(OR(K6="",J6=""),"",IF(J6="PayPay",ROUND(K6*0.05),IF(J6="エコリング",0,ROUND(K6*0.1))))</f>
+        <f>IF(OR(K6="",J6=""),"",IF(J6="エコリング","",IF(J6="PayPay",ROUND(K6*0.05),ROUND(K6*0.1))))</f>
         <v/>
       </c>
       <c r="M6" s="4" t="n"/>
@@ -904,7 +904,7 @@
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="8">
-        <f>IF(OR(K7="",J7=""),"",IF(J7="PayPay",ROUND(K7*0.05),IF(J7="エコリング",0,ROUND(K7*0.1))))</f>
+        <f>IF(OR(K7="",J7=""),"",IF(J7="エコリング","",IF(J7="PayPay",ROUND(K7*0.05),ROUND(K7*0.1))))</f>
         <v/>
       </c>
       <c r="M7" s="8" t="n"/>
@@ -956,7 +956,7 @@
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4">
-        <f>IF(OR(K8="",J8=""),"",IF(J8="PayPay",ROUND(K8*0.05),IF(J8="エコリング",0,ROUND(K8*0.1))))</f>
+        <f>IF(OR(K8="",J8=""),"",IF(J8="エコリング","",IF(J8="PayPay",ROUND(K8*0.05),ROUND(K8*0.1))))</f>
         <v/>
       </c>
       <c r="M8" s="4" t="n"/>
@@ -1008,7 +1008,7 @@
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="8">
-        <f>IF(OR(K9="",J9=""),"",IF(J9="PayPay",ROUND(K9*0.05),IF(J9="エコリング",0,ROUND(K9*0.1))))</f>
+        <f>IF(OR(K9="",J9=""),"",IF(J9="エコリング","",IF(J9="PayPay",ROUND(K9*0.05),ROUND(K9*0.1))))</f>
         <v/>
       </c>
       <c r="M9" s="8" t="n"/>
@@ -1060,7 +1060,7 @@
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4">
-        <f>IF(OR(K10="",J10=""),"",IF(J10="PayPay",ROUND(K10*0.05),IF(J10="エコリング",0,ROUND(K10*0.1))))</f>
+        <f>IF(OR(K10="",J10=""),"",IF(J10="エコリング","",IF(J10="PayPay",ROUND(K10*0.05),ROUND(K10*0.1))))</f>
         <v/>
       </c>
       <c r="M10" s="4" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="8">
-        <f>IF(OR(K11="",J11=""),"",IF(J11="PayPay",ROUND(K11*0.05),IF(J11="エコリング",0,ROUND(K11*0.1))))</f>
+        <f>IF(OR(K11="",J11=""),"",IF(J11="エコリング","",IF(J11="PayPay",ROUND(K11*0.05),ROUND(K11*0.1))))</f>
         <v/>
       </c>
       <c r="M11" s="8" t="n"/>
@@ -1168,7 +1168,7 @@
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4">
-        <f>IF(OR(K12="",J12=""),"",IF(J12="PayPay",ROUND(K12*0.05),IF(J12="エコリング",0,ROUND(K12*0.1))))</f>
+        <f>IF(OR(K12="",J12=""),"",IF(J12="エコリング","",IF(J12="PayPay",ROUND(K12*0.05),ROUND(K12*0.1))))</f>
         <v/>
       </c>
       <c r="M12" s="4" t="n"/>
@@ -1220,7 +1220,7 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="8">
-        <f>IF(OR(K13="",J13=""),"",IF(J13="PayPay",ROUND(K13*0.05),IF(J13="エコリング",0,ROUND(K13*0.1))))</f>
+        <f>IF(OR(K13="",J13=""),"",IF(J13="エコリング","",IF(J13="PayPay",ROUND(K13*0.05),ROUND(K13*0.1))))</f>
         <v/>
       </c>
       <c r="M13" s="8" t="n"/>
@@ -1272,7 +1272,7 @@
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4">
-        <f>IF(OR(K14="",J14=""),"",IF(J14="PayPay",ROUND(K14*0.05),IF(J14="エコリング",0,ROUND(K14*0.1))))</f>
+        <f>IF(OR(K14="",J14=""),"",IF(J14="エコリング","",IF(J14="PayPay",ROUND(K14*0.05),ROUND(K14*0.1))))</f>
         <v/>
       </c>
       <c r="M14" s="4" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="8">
-        <f>IF(OR(K15="",J15=""),"",IF(J15="PayPay",ROUND(K15*0.05),IF(J15="エコリング",0,ROUND(K15*0.1))))</f>
+        <f>IF(OR(K15="",J15=""),"",IF(J15="エコリング","",IF(J15="PayPay",ROUND(K15*0.05),ROUND(K15*0.1))))</f>
         <v/>
       </c>
       <c r="M15" s="8" t="n"/>
@@ -1380,7 +1380,7 @@
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4">
-        <f>IF(OR(K16="",J16=""),"",IF(J16="PayPay",ROUND(K16*0.05),IF(J16="エコリング",0,ROUND(K16*0.1))))</f>
+        <f>IF(OR(K16="",J16=""),"",IF(J16="エコリング","",IF(J16="PayPay",ROUND(K16*0.05),ROUND(K16*0.1))))</f>
         <v/>
       </c>
       <c r="M16" s="4" t="n"/>
@@ -1432,7 +1432,7 @@
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="8">
-        <f>IF(OR(K17="",J17=""),"",IF(J17="PayPay",ROUND(K17*0.05),IF(J17="エコリング",0,ROUND(K17*0.1))))</f>
+        <f>IF(OR(K17="",J17=""),"",IF(J17="エコリング","",IF(J17="PayPay",ROUND(K17*0.05),ROUND(K17*0.1))))</f>
         <v/>
       </c>
       <c r="M17" s="8" t="n"/>
@@ -1484,7 +1484,7 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4">
-        <f>IF(OR(K18="",J18=""),"",IF(J18="PayPay",ROUND(K18*0.05),IF(J18="エコリング",0,ROUND(K18*0.1))))</f>
+        <f>IF(OR(K18="",J18=""),"",IF(J18="エコリング","",IF(J18="PayPay",ROUND(K18*0.05),ROUND(K18*0.1))))</f>
         <v/>
       </c>
       <c r="M18" s="4" t="n"/>
@@ -1536,7 +1536,7 @@
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="8">
-        <f>IF(OR(K19="",J19=""),"",IF(J19="PayPay",ROUND(K19*0.05),IF(J19="エコリング",0,ROUND(K19*0.1))))</f>
+        <f>IF(OR(K19="",J19=""),"",IF(J19="エコリング","",IF(J19="PayPay",ROUND(K19*0.05),ROUND(K19*0.1))))</f>
         <v/>
       </c>
       <c r="M19" s="8" t="n"/>
@@ -1566,7 +1566,7 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4">
-        <f>IF(OR(K20="",J20=""),"",IF(J20="PayPay",ROUND(K20*0.05),IF(J20="エコリング",0,ROUND(K20*0.1))))</f>
+        <f>IF(OR(K20="",J20=""),"",IF(J20="エコリング","",IF(J20="PayPay",ROUND(K20*0.05),ROUND(K20*0.1))))</f>
         <v/>
       </c>
       <c r="M20" s="4" t="n"/>
@@ -1596,7 +1596,7 @@
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="8">
-        <f>IF(OR(K21="",J21=""),"",IF(J21="PayPay",ROUND(K21*0.05),IF(J21="エコリング",0,ROUND(K21*0.1))))</f>
+        <f>IF(OR(K21="",J21=""),"",IF(J21="エコリング","",IF(J21="PayPay",ROUND(K21*0.05),ROUND(K21*0.1))))</f>
         <v/>
       </c>
       <c r="M21" s="8" t="n"/>
@@ -1626,7 +1626,7 @@
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="4" t="n"/>
       <c r="L22" s="4">
-        <f>IF(OR(K22="",J22=""),"",IF(J22="PayPay",ROUND(K22*0.05),IF(J22="エコリング",0,ROUND(K22*0.1))))</f>
+        <f>IF(OR(K22="",J22=""),"",IF(J22="エコリング","",IF(J22="PayPay",ROUND(K22*0.05),ROUND(K22*0.1))))</f>
         <v/>
       </c>
       <c r="M22" s="4" t="n"/>
@@ -1656,7 +1656,7 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="8">
-        <f>IF(OR(K23="",J23=""),"",IF(J23="PayPay",ROUND(K23*0.05),IF(J23="エコリング",0,ROUND(K23*0.1))))</f>
+        <f>IF(OR(K23="",J23=""),"",IF(J23="エコリング","",IF(J23="PayPay",ROUND(K23*0.05),ROUND(K23*0.1))))</f>
         <v/>
       </c>
       <c r="M23" s="8" t="n"/>
@@ -1686,7 +1686,7 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4">
-        <f>IF(OR(K24="",J24=""),"",IF(J24="PayPay",ROUND(K24*0.05),IF(J24="エコリング",0,ROUND(K24*0.1))))</f>
+        <f>IF(OR(K24="",J24=""),"",IF(J24="エコリング","",IF(J24="PayPay",ROUND(K24*0.05),ROUND(K24*0.1))))</f>
         <v/>
       </c>
       <c r="M24" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="8">
-        <f>IF(OR(K25="",J25=""),"",IF(J25="PayPay",ROUND(K25*0.05),IF(J25="エコリング",0,ROUND(K25*0.1))))</f>
+        <f>IF(OR(K25="",J25=""),"",IF(J25="エコリング","",IF(J25="PayPay",ROUND(K25*0.05),ROUND(K25*0.1))))</f>
         <v/>
       </c>
       <c r="M25" s="8" t="n"/>
@@ -1746,7 +1746,7 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4">
-        <f>IF(OR(K26="",J26=""),"",IF(J26="PayPay",ROUND(K26*0.05),IF(J26="エコリング",0,ROUND(K26*0.1))))</f>
+        <f>IF(OR(K26="",J26=""),"",IF(J26="エコリング","",IF(J26="PayPay",ROUND(K26*0.05),ROUND(K26*0.1))))</f>
         <v/>
       </c>
       <c r="M26" s="4" t="n"/>
@@ -1776,7 +1776,7 @@
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="8">
-        <f>IF(OR(K27="",J27=""),"",IF(J27="PayPay",ROUND(K27*0.05),IF(J27="エコリング",0,ROUND(K27*0.1))))</f>
+        <f>IF(OR(K27="",J27=""),"",IF(J27="エコリング","",IF(J27="PayPay",ROUND(K27*0.05),ROUND(K27*0.1))))</f>
         <v/>
       </c>
       <c r="M27" s="8" t="n"/>
@@ -1806,7 +1806,7 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4">
-        <f>IF(OR(K28="",J28=""),"",IF(J28="PayPay",ROUND(K28*0.05),IF(J28="エコリング",0,ROUND(K28*0.1))))</f>
+        <f>IF(OR(K28="",J28=""),"",IF(J28="エコリング","",IF(J28="PayPay",ROUND(K28*0.05),ROUND(K28*0.1))))</f>
         <v/>
       </c>
       <c r="M28" s="4" t="n"/>
@@ -1836,7 +1836,7 @@
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="8">
-        <f>IF(OR(K29="",J29=""),"",IF(J29="PayPay",ROUND(K29*0.05),IF(J29="エコリング",0,ROUND(K29*0.1))))</f>
+        <f>IF(OR(K29="",J29=""),"",IF(J29="エコリング","",IF(J29="PayPay",ROUND(K29*0.05),ROUND(K29*0.1))))</f>
         <v/>
       </c>
       <c r="M29" s="8" t="n"/>
@@ -1866,7 +1866,7 @@
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4">
-        <f>IF(OR(K30="",J30=""),"",IF(J30="PayPay",ROUND(K30*0.05),IF(J30="エコリング",0,ROUND(K30*0.1))))</f>
+        <f>IF(OR(K30="",J30=""),"",IF(J30="エコリング","",IF(J30="PayPay",ROUND(K30*0.05),ROUND(K30*0.1))))</f>
         <v/>
       </c>
       <c r="M30" s="4" t="n"/>
@@ -1896,7 +1896,7 @@
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="8">
-        <f>IF(OR(K31="",J31=""),"",IF(J31="PayPay",ROUND(K31*0.05),IF(J31="エコリング",0,ROUND(K31*0.1))))</f>
+        <f>IF(OR(K31="",J31=""),"",IF(J31="エコリング","",IF(J31="PayPay",ROUND(K31*0.05),ROUND(K31*0.1))))</f>
         <v/>
       </c>
       <c r="M31" s="8" t="n"/>
@@ -1926,7 +1926,7 @@
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4">
-        <f>IF(OR(K32="",J32=""),"",IF(J32="PayPay",ROUND(K32*0.05),IF(J32="エコリング",0,ROUND(K32*0.1))))</f>
+        <f>IF(OR(K32="",J32=""),"",IF(J32="エコリング","",IF(J32="PayPay",ROUND(K32*0.05),ROUND(K32*0.1))))</f>
         <v/>
       </c>
       <c r="M32" s="4" t="n"/>
@@ -1956,7 +1956,7 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="8">
-        <f>IF(OR(K33="",J33=""),"",IF(J33="PayPay",ROUND(K33*0.05),IF(J33="エコリング",0,ROUND(K33*0.1))))</f>
+        <f>IF(OR(K33="",J33=""),"",IF(J33="エコリング","",IF(J33="PayPay",ROUND(K33*0.05),ROUND(K33*0.1))))</f>
         <v/>
       </c>
       <c r="M33" s="8" t="n"/>
@@ -1986,7 +1986,7 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="4" t="n"/>
       <c r="L34" s="4">
-        <f>IF(OR(K34="",J34=""),"",IF(J34="PayPay",ROUND(K34*0.05),IF(J34="エコリング",0,ROUND(K34*0.1))))</f>
+        <f>IF(OR(K34="",J34=""),"",IF(J34="エコリング","",IF(J34="PayPay",ROUND(K34*0.05),ROUND(K34*0.1))))</f>
         <v/>
       </c>
       <c r="M34" s="4" t="n"/>
@@ -2016,7 +2016,7 @@
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="8">
-        <f>IF(OR(K35="",J35=""),"",IF(J35="PayPay",ROUND(K35*0.05),IF(J35="エコリング",0,ROUND(K35*0.1))))</f>
+        <f>IF(OR(K35="",J35=""),"",IF(J35="エコリング","",IF(J35="PayPay",ROUND(K35*0.05),ROUND(K35*0.1))))</f>
         <v/>
       </c>
       <c r="M35" s="8" t="n"/>
@@ -2046,7 +2046,7 @@
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4">
-        <f>IF(OR(K36="",J36=""),"",IF(J36="PayPay",ROUND(K36*0.05),IF(J36="エコリング",0,ROUND(K36*0.1))))</f>
+        <f>IF(OR(K36="",J36=""),"",IF(J36="エコリング","",IF(J36="PayPay",ROUND(K36*0.05),ROUND(K36*0.1))))</f>
         <v/>
       </c>
       <c r="M36" s="4" t="n"/>
@@ -2076,7 +2076,7 @@
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="8">
-        <f>IF(OR(K37="",J37=""),"",IF(J37="PayPay",ROUND(K37*0.05),IF(J37="エコリング",0,ROUND(K37*0.1))))</f>
+        <f>IF(OR(K37="",J37=""),"",IF(J37="エコリング","",IF(J37="PayPay",ROUND(K37*0.05),ROUND(K37*0.1))))</f>
         <v/>
       </c>
       <c r="M37" s="8" t="n"/>
@@ -2106,7 +2106,7 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4">
-        <f>IF(OR(K38="",J38=""),"",IF(J38="PayPay",ROUND(K38*0.05),IF(J38="エコリング",0,ROUND(K38*0.1))))</f>
+        <f>IF(OR(K38="",J38=""),"",IF(J38="エコリング","",IF(J38="PayPay",ROUND(K38*0.05),ROUND(K38*0.1))))</f>
         <v/>
       </c>
       <c r="M38" s="4" t="n"/>
@@ -2136,7 +2136,7 @@
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="8">
-        <f>IF(OR(K39="",J39=""),"",IF(J39="PayPay",ROUND(K39*0.05),IF(J39="エコリング",0,ROUND(K39*0.1))))</f>
+        <f>IF(OR(K39="",J39=""),"",IF(J39="エコリング","",IF(J39="PayPay",ROUND(K39*0.05),ROUND(K39*0.1))))</f>
         <v/>
       </c>
       <c r="M39" s="8" t="n"/>
@@ -2166,7 +2166,7 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4">
-        <f>IF(OR(K40="",J40=""),"",IF(J40="PayPay",ROUND(K40*0.05),IF(J40="エコリング",0,ROUND(K40*0.1))))</f>
+        <f>IF(OR(K40="",J40=""),"",IF(J40="エコリング","",IF(J40="PayPay",ROUND(K40*0.05),ROUND(K40*0.1))))</f>
         <v/>
       </c>
       <c r="M40" s="4" t="n"/>
@@ -2196,7 +2196,7 @@
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="8">
-        <f>IF(OR(K41="",J41=""),"",IF(J41="PayPay",ROUND(K41*0.05),IF(J41="エコリング",0,ROUND(K41*0.1))))</f>
+        <f>IF(OR(K41="",J41=""),"",IF(J41="エコリング","",IF(J41="PayPay",ROUND(K41*0.05),ROUND(K41*0.1))))</f>
         <v/>
       </c>
       <c r="M41" s="8" t="n"/>
@@ -2226,7 +2226,7 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4">
-        <f>IF(OR(K42="",J42=""),"",IF(J42="PayPay",ROUND(K42*0.05),IF(J42="エコリング",0,ROUND(K42*0.1))))</f>
+        <f>IF(OR(K42="",J42=""),"",IF(J42="エコリング","",IF(J42="PayPay",ROUND(K42*0.05),ROUND(K42*0.1))))</f>
         <v/>
       </c>
       <c r="M42" s="4" t="n"/>
@@ -2256,7 +2256,7 @@
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="8">
-        <f>IF(OR(K43="",J43=""),"",IF(J43="PayPay",ROUND(K43*0.05),IF(J43="エコリング",0,ROUND(K43*0.1))))</f>
+        <f>IF(OR(K43="",J43=""),"",IF(J43="エコリング","",IF(J43="PayPay",ROUND(K43*0.05),ROUND(K43*0.1))))</f>
         <v/>
       </c>
       <c r="M43" s="8" t="n"/>
@@ -2286,7 +2286,7 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4">
-        <f>IF(OR(K44="",J44=""),"",IF(J44="PayPay",ROUND(K44*0.05),IF(J44="エコリング",0,ROUND(K44*0.1))))</f>
+        <f>IF(OR(K44="",J44=""),"",IF(J44="エコリング","",IF(J44="PayPay",ROUND(K44*0.05),ROUND(K44*0.1))))</f>
         <v/>
       </c>
       <c r="M44" s="4" t="n"/>
@@ -2316,7 +2316,7 @@
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="8" t="n"/>
       <c r="L45" s="8">
-        <f>IF(OR(K45="",J45=""),"",IF(J45="PayPay",ROUND(K45*0.05),IF(J45="エコリング",0,ROUND(K45*0.1))))</f>
+        <f>IF(OR(K45="",J45=""),"",IF(J45="エコリング","",IF(J45="PayPay",ROUND(K45*0.05),ROUND(K45*0.1))))</f>
         <v/>
       </c>
       <c r="M45" s="8" t="n"/>
@@ -2346,7 +2346,7 @@
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4">
-        <f>IF(OR(K46="",J46=""),"",IF(J46="PayPay",ROUND(K46*0.05),IF(J46="エコリング",0,ROUND(K46*0.1))))</f>
+        <f>IF(OR(K46="",J46=""),"",IF(J46="エコリング","",IF(J46="PayPay",ROUND(K46*0.05),ROUND(K46*0.1))))</f>
         <v/>
       </c>
       <c r="M46" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="8" t="n"/>
       <c r="L47" s="8">
-        <f>IF(OR(K47="",J47=""),"",IF(J47="PayPay",ROUND(K47*0.05),IF(J47="エコリング",0,ROUND(K47*0.1))))</f>
+        <f>IF(OR(K47="",J47=""),"",IF(J47="エコリング","",IF(J47="PayPay",ROUND(K47*0.05),ROUND(K47*0.1))))</f>
         <v/>
       </c>
       <c r="M47" s="8" t="n"/>
@@ -2406,7 +2406,7 @@
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4">
-        <f>IF(OR(K48="",J48=""),"",IF(J48="PayPay",ROUND(K48*0.05),IF(J48="エコリング",0,ROUND(K48*0.1))))</f>
+        <f>IF(OR(K48="",J48=""),"",IF(J48="エコリング","",IF(J48="PayPay",ROUND(K48*0.05),ROUND(K48*0.1))))</f>
         <v/>
       </c>
       <c r="M48" s="4" t="n"/>
@@ -2436,7 +2436,7 @@
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="8">
-        <f>IF(OR(K49="",J49=""),"",IF(J49="PayPay",ROUND(K49*0.05),IF(J49="エコリング",0,ROUND(K49*0.1))))</f>
+        <f>IF(OR(K49="",J49=""),"",IF(J49="エコリング","",IF(J49="PayPay",ROUND(K49*0.05),ROUND(K49*0.1))))</f>
         <v/>
       </c>
       <c r="M49" s="8" t="n"/>
@@ -2466,7 +2466,7 @@
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4">
-        <f>IF(OR(K50="",J50=""),"",IF(J50="PayPay",ROUND(K50*0.05),IF(J50="エコリング",0,ROUND(K50*0.1))))</f>
+        <f>IF(OR(K50="",J50=""),"",IF(J50="エコリング","",IF(J50="PayPay",ROUND(K50*0.05),ROUND(K50*0.1))))</f>
         <v/>
       </c>
       <c r="M50" s="4" t="n"/>
@@ -2496,7 +2496,7 @@
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="8">
-        <f>IF(OR(K51="",J51=""),"",IF(J51="PayPay",ROUND(K51*0.05),IF(J51="エコリング",0,ROUND(K51*0.1))))</f>
+        <f>IF(OR(K51="",J51=""),"",IF(J51="エコリング","",IF(J51="PayPay",ROUND(K51*0.05),ROUND(K51*0.1))))</f>
         <v/>
       </c>
       <c r="M51" s="8" t="n"/>
@@ -2526,7 +2526,7 @@
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4">
-        <f>IF(OR(K52="",J52=""),"",IF(J52="PayPay",ROUND(K52*0.05),IF(J52="エコリング",0,ROUND(K52*0.1))))</f>
+        <f>IF(OR(K52="",J52=""),"",IF(J52="エコリング","",IF(J52="PayPay",ROUND(K52*0.05),ROUND(K52*0.1))))</f>
         <v/>
       </c>
       <c r="M52" s="4" t="n"/>
@@ -2556,7 +2556,7 @@
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="8">
-        <f>IF(OR(K53="",J53=""),"",IF(J53="PayPay",ROUND(K53*0.05),IF(J53="エコリング",0,ROUND(K53*0.1))))</f>
+        <f>IF(OR(K53="",J53=""),"",IF(J53="エコリング","",IF(J53="PayPay",ROUND(K53*0.05),ROUND(K53*0.1))))</f>
         <v/>
       </c>
       <c r="M53" s="8" t="n"/>
@@ -2586,7 +2586,7 @@
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="4" t="n"/>
       <c r="L54" s="4">
-        <f>IF(OR(K54="",J54=""),"",IF(J54="PayPay",ROUND(K54*0.05),IF(J54="エコリング",0,ROUND(K54*0.1))))</f>
+        <f>IF(OR(K54="",J54=""),"",IF(J54="エコリング","",IF(J54="PayPay",ROUND(K54*0.05),ROUND(K54*0.1))))</f>
         <v/>
       </c>
       <c r="M54" s="4" t="n"/>
@@ -2616,7 +2616,7 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="8">
-        <f>IF(OR(K55="",J55=""),"",IF(J55="PayPay",ROUND(K55*0.05),IF(J55="エコリング",0,ROUND(K55*0.1))))</f>
+        <f>IF(OR(K55="",J55=""),"",IF(J55="エコリング","",IF(J55="PayPay",ROUND(K55*0.05),ROUND(K55*0.1))))</f>
         <v/>
       </c>
       <c r="M55" s="8" t="n"/>
@@ -2646,7 +2646,7 @@
       <c r="J56" s="2" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4">
-        <f>IF(OR(K56="",J56=""),"",IF(J56="PayPay",ROUND(K56*0.05),IF(J56="エコリング",0,ROUND(K56*0.1))))</f>
+        <f>IF(OR(K56="",J56=""),"",IF(J56="エコリング","",IF(J56="PayPay",ROUND(K56*0.05),ROUND(K56*0.1))))</f>
         <v/>
       </c>
       <c r="M56" s="4" t="n"/>
@@ -2676,7 +2676,7 @@
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="8">
-        <f>IF(OR(K57="",J57=""),"",IF(J57="PayPay",ROUND(K57*0.05),IF(J57="エコリング",0,ROUND(K57*0.1))))</f>
+        <f>IF(OR(K57="",J57=""),"",IF(J57="エコリング","",IF(J57="PayPay",ROUND(K57*0.05),ROUND(K57*0.1))))</f>
         <v/>
       </c>
       <c r="M57" s="8" t="n"/>
@@ -2706,7 +2706,7 @@
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4">
-        <f>IF(OR(K58="",J58=""),"",IF(J58="PayPay",ROUND(K58*0.05),IF(J58="エコリング",0,ROUND(K58*0.1))))</f>
+        <f>IF(OR(K58="",J58=""),"",IF(J58="エコリング","",IF(J58="PayPay",ROUND(K58*0.05),ROUND(K58*0.1))))</f>
         <v/>
       </c>
       <c r="M58" s="4" t="n"/>
@@ -2736,7 +2736,7 @@
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="8">
-        <f>IF(OR(K59="",J59=""),"",IF(J59="PayPay",ROUND(K59*0.05),IF(J59="エコリング",0,ROUND(K59*0.1))))</f>
+        <f>IF(OR(K59="",J59=""),"",IF(J59="エコリング","",IF(J59="PayPay",ROUND(K59*0.05),ROUND(K59*0.1))))</f>
         <v/>
       </c>
       <c r="M59" s="8" t="n"/>
@@ -2766,7 +2766,7 @@
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="4" t="n"/>
       <c r="L60" s="4">
-        <f>IF(OR(K60="",J60=""),"",IF(J60="PayPay",ROUND(K60*0.05),IF(J60="エコリング",0,ROUND(K60*0.1))))</f>
+        <f>IF(OR(K60="",J60=""),"",IF(J60="エコリング","",IF(J60="PayPay",ROUND(K60*0.05),ROUND(K60*0.1))))</f>
         <v/>
       </c>
       <c r="M60" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="8" t="n"/>
       <c r="L61" s="8">
-        <f>IF(OR(K61="",J61=""),"",IF(J61="PayPay",ROUND(K61*0.05),IF(J61="エコリング",0,ROUND(K61*0.1))))</f>
+        <f>IF(OR(K61="",J61=""),"",IF(J61="エコリング","",IF(J61="PayPay",ROUND(K61*0.05),ROUND(K61*0.1))))</f>
         <v/>
       </c>
       <c r="M61" s="8" t="n"/>
@@ -2826,7 +2826,7 @@
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="4" t="n"/>
       <c r="L62" s="4">
-        <f>IF(OR(K62="",J62=""),"",IF(J62="PayPay",ROUND(K62*0.05),IF(J62="エコリング",0,ROUND(K62*0.1))))</f>
+        <f>IF(OR(K62="",J62=""),"",IF(J62="エコリング","",IF(J62="PayPay",ROUND(K62*0.05),ROUND(K62*0.1))))</f>
         <v/>
       </c>
       <c r="M62" s="4" t="n"/>
@@ -2856,7 +2856,7 @@
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="8" t="n"/>
       <c r="L63" s="8">
-        <f>IF(OR(K63="",J63=""),"",IF(J63="PayPay",ROUND(K63*0.05),IF(J63="エコリング",0,ROUND(K63*0.1))))</f>
+        <f>IF(OR(K63="",J63=""),"",IF(J63="エコリング","",IF(J63="PayPay",ROUND(K63*0.05),ROUND(K63*0.1))))</f>
         <v/>
       </c>
       <c r="M63" s="8" t="n"/>
@@ -2886,7 +2886,7 @@
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4">
-        <f>IF(OR(K64="",J64=""),"",IF(J64="PayPay",ROUND(K64*0.05),IF(J64="エコリング",0,ROUND(K64*0.1))))</f>
+        <f>IF(OR(K64="",J64=""),"",IF(J64="エコリング","",IF(J64="PayPay",ROUND(K64*0.05),ROUND(K64*0.1))))</f>
         <v/>
       </c>
       <c r="M64" s="4" t="n"/>
@@ -2916,7 +2916,7 @@
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="8" t="n"/>
       <c r="L65" s="8">
-        <f>IF(OR(K65="",J65=""),"",IF(J65="PayPay",ROUND(K65*0.05),IF(J65="エコリング",0,ROUND(K65*0.1))))</f>
+        <f>IF(OR(K65="",J65=""),"",IF(J65="エコリング","",IF(J65="PayPay",ROUND(K65*0.05),ROUND(K65*0.1))))</f>
         <v/>
       </c>
       <c r="M65" s="8" t="n"/>
@@ -2946,7 +2946,7 @@
       <c r="J66" s="2" t="n"/>
       <c r="K66" s="4" t="n"/>
       <c r="L66" s="4">
-        <f>IF(OR(K66="",J66=""),"",IF(J66="PayPay",ROUND(K66*0.05),IF(J66="エコリング",0,ROUND(K66*0.1))))</f>
+        <f>IF(OR(K66="",J66=""),"",IF(J66="エコリング","",IF(J66="PayPay",ROUND(K66*0.05),ROUND(K66*0.1))))</f>
         <v/>
       </c>
       <c r="M66" s="4" t="n"/>
@@ -2976,7 +2976,7 @@
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="8" t="n"/>
       <c r="L67" s="8">
-        <f>IF(OR(K67="",J67=""),"",IF(J67="PayPay",ROUND(K67*0.05),IF(J67="エコリング",0,ROUND(K67*0.1))))</f>
+        <f>IF(OR(K67="",J67=""),"",IF(J67="エコリング","",IF(J67="PayPay",ROUND(K67*0.05),ROUND(K67*0.1))))</f>
         <v/>
       </c>
       <c r="M67" s="8" t="n"/>
@@ -3006,7 +3006,7 @@
       <c r="J68" s="2" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4">
-        <f>IF(OR(K68="",J68=""),"",IF(J68="PayPay",ROUND(K68*0.05),IF(J68="エコリング",0,ROUND(K68*0.1))))</f>
+        <f>IF(OR(K68="",J68=""),"",IF(J68="エコリング","",IF(J68="PayPay",ROUND(K68*0.05),ROUND(K68*0.1))))</f>
         <v/>
       </c>
       <c r="M68" s="4" t="n"/>
@@ -3036,7 +3036,7 @@
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="8" t="n"/>
       <c r="L69" s="8">
-        <f>IF(OR(K69="",J69=""),"",IF(J69="PayPay",ROUND(K69*0.05),IF(J69="エコリング",0,ROUND(K69*0.1))))</f>
+        <f>IF(OR(K69="",J69=""),"",IF(J69="エコリング","",IF(J69="PayPay",ROUND(K69*0.05),ROUND(K69*0.1))))</f>
         <v/>
       </c>
       <c r="M69" s="8" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4">
-        <f>IF(OR(K70="",J70=""),"",IF(J70="PayPay",ROUND(K70*0.05),IF(J70="エコリング",0,ROUND(K70*0.1))))</f>
+        <f>IF(OR(K70="",J70=""),"",IF(J70="エコリング","",IF(J70="PayPay",ROUND(K70*0.05),ROUND(K70*0.1))))</f>
         <v/>
       </c>
       <c r="M70" s="4" t="n"/>
@@ -3096,7 +3096,7 @@
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="8" t="n"/>
       <c r="L71" s="8">
-        <f>IF(OR(K71="",J71=""),"",IF(J71="PayPay",ROUND(K71*0.05),IF(J71="エコリング",0,ROUND(K71*0.1))))</f>
+        <f>IF(OR(K71="",J71=""),"",IF(J71="エコリング","",IF(J71="PayPay",ROUND(K71*0.05),ROUND(K71*0.1))))</f>
         <v/>
       </c>
       <c r="M71" s="8" t="n"/>
@@ -3126,7 +3126,7 @@
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4">
-        <f>IF(OR(K72="",J72=""),"",IF(J72="PayPay",ROUND(K72*0.05),IF(J72="エコリング",0,ROUND(K72*0.1))))</f>
+        <f>IF(OR(K72="",J72=""),"",IF(J72="エコリング","",IF(J72="PayPay",ROUND(K72*0.05),ROUND(K72*0.1))))</f>
         <v/>
       </c>
       <c r="M72" s="4" t="n"/>
@@ -3156,7 +3156,7 @@
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="8" t="n"/>
       <c r="L73" s="8">
-        <f>IF(OR(K73="",J73=""),"",IF(J73="PayPay",ROUND(K73*0.05),IF(J73="エコリング",0,ROUND(K73*0.1))))</f>
+        <f>IF(OR(K73="",J73=""),"",IF(J73="エコリング","",IF(J73="PayPay",ROUND(K73*0.05),ROUND(K73*0.1))))</f>
         <v/>
       </c>
       <c r="M73" s="8" t="n"/>
@@ -3186,7 +3186,7 @@
       <c r="J74" s="2" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4">
-        <f>IF(OR(K74="",J74=""),"",IF(J74="PayPay",ROUND(K74*0.05),IF(J74="エコリング",0,ROUND(K74*0.1))))</f>
+        <f>IF(OR(K74="",J74=""),"",IF(J74="エコリング","",IF(J74="PayPay",ROUND(K74*0.05),ROUND(K74*0.1))))</f>
         <v/>
       </c>
       <c r="M74" s="4" t="n"/>
@@ -3216,7 +3216,7 @@
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="8" t="n"/>
       <c r="L75" s="8">
-        <f>IF(OR(K75="",J75=""),"",IF(J75="PayPay",ROUND(K75*0.05),IF(J75="エコリング",0,ROUND(K75*0.1))))</f>
+        <f>IF(OR(K75="",J75=""),"",IF(J75="エコリング","",IF(J75="PayPay",ROUND(K75*0.05),ROUND(K75*0.1))))</f>
         <v/>
       </c>
       <c r="M75" s="8" t="n"/>
@@ -3246,7 +3246,7 @@
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4">
-        <f>IF(OR(K76="",J76=""),"",IF(J76="PayPay",ROUND(K76*0.05),IF(J76="エコリング",0,ROUND(K76*0.1))))</f>
+        <f>IF(OR(K76="",J76=""),"",IF(J76="エコリング","",IF(J76="PayPay",ROUND(K76*0.05),ROUND(K76*0.1))))</f>
         <v/>
       </c>
       <c r="M76" s="4" t="n"/>
@@ -3276,7 +3276,7 @@
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="8" t="n"/>
       <c r="L77" s="8">
-        <f>IF(OR(K77="",J77=""),"",IF(J77="PayPay",ROUND(K77*0.05),IF(J77="エコリング",0,ROUND(K77*0.1))))</f>
+        <f>IF(OR(K77="",J77=""),"",IF(J77="エコリング","",IF(J77="PayPay",ROUND(K77*0.05),ROUND(K77*0.1))))</f>
         <v/>
       </c>
       <c r="M77" s="8" t="n"/>
@@ -3306,7 +3306,7 @@
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="4" t="n"/>
       <c r="L78" s="4">
-        <f>IF(OR(K78="",J78=""),"",IF(J78="PayPay",ROUND(K78*0.05),IF(J78="エコリング",0,ROUND(K78*0.1))))</f>
+        <f>IF(OR(K78="",J78=""),"",IF(J78="エコリング","",IF(J78="PayPay",ROUND(K78*0.05),ROUND(K78*0.1))))</f>
         <v/>
       </c>
       <c r="M78" s="4" t="n"/>
@@ -3336,7 +3336,7 @@
       <c r="J79" s="6" t="n"/>
       <c r="K79" s="8" t="n"/>
       <c r="L79" s="8">
-        <f>IF(OR(K79="",J79=""),"",IF(J79="PayPay",ROUND(K79*0.05),IF(J79="エコリング",0,ROUND(K79*0.1))))</f>
+        <f>IF(OR(K79="",J79=""),"",IF(J79="エコリング","",IF(J79="PayPay",ROUND(K79*0.05),ROUND(K79*0.1))))</f>
         <v/>
       </c>
       <c r="M79" s="8" t="n"/>
@@ -3366,7 +3366,7 @@
       <c r="J80" s="2" t="n"/>
       <c r="K80" s="4" t="n"/>
       <c r="L80" s="4">
-        <f>IF(OR(K80="",J80=""),"",IF(J80="PayPay",ROUND(K80*0.05),IF(J80="エコリング",0,ROUND(K80*0.1))))</f>
+        <f>IF(OR(K80="",J80=""),"",IF(J80="エコリング","",IF(J80="PayPay",ROUND(K80*0.05),ROUND(K80*0.1))))</f>
         <v/>
       </c>
       <c r="M80" s="4" t="n"/>
@@ -3396,7 +3396,7 @@
       <c r="J81" s="6" t="n"/>
       <c r="K81" s="8" t="n"/>
       <c r="L81" s="8">
-        <f>IF(OR(K81="",J81=""),"",IF(J81="PayPay",ROUND(K81*0.05),IF(J81="エコリング",0,ROUND(K81*0.1))))</f>
+        <f>IF(OR(K81="",J81=""),"",IF(J81="エコリング","",IF(J81="PayPay",ROUND(K81*0.05),ROUND(K81*0.1))))</f>
         <v/>
       </c>
       <c r="M81" s="8" t="n"/>
@@ -3426,7 +3426,7 @@
       <c r="J82" s="2" t="n"/>
       <c r="K82" s="4" t="n"/>
       <c r="L82" s="4">
-        <f>IF(OR(K82="",J82=""),"",IF(J82="PayPay",ROUND(K82*0.05),IF(J82="エコリング",0,ROUND(K82*0.1))))</f>
+        <f>IF(OR(K82="",J82=""),"",IF(J82="エコリング","",IF(J82="PayPay",ROUND(K82*0.05),ROUND(K82*0.1))))</f>
         <v/>
       </c>
       <c r="M82" s="4" t="n"/>
@@ -3456,7 +3456,7 @@
       <c r="J83" s="6" t="n"/>
       <c r="K83" s="8" t="n"/>
       <c r="L83" s="8">
-        <f>IF(OR(K83="",J83=""),"",IF(J83="PayPay",ROUND(K83*0.05),IF(J83="エコリング",0,ROUND(K83*0.1))))</f>
+        <f>IF(OR(K83="",J83=""),"",IF(J83="エコリング","",IF(J83="PayPay",ROUND(K83*0.05),ROUND(K83*0.1))))</f>
         <v/>
       </c>
       <c r="M83" s="8" t="n"/>
@@ -3486,7 +3486,7 @@
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4">
-        <f>IF(OR(K84="",J84=""),"",IF(J84="PayPay",ROUND(K84*0.05),IF(J84="エコリング",0,ROUND(K84*0.1))))</f>
+        <f>IF(OR(K84="",J84=""),"",IF(J84="エコリング","",IF(J84="PayPay",ROUND(K84*0.05),ROUND(K84*0.1))))</f>
         <v/>
       </c>
       <c r="M84" s="4" t="n"/>
@@ -3516,7 +3516,7 @@
       <c r="J85" s="6" t="n"/>
       <c r="K85" s="8" t="n"/>
       <c r="L85" s="8">
-        <f>IF(OR(K85="",J85=""),"",IF(J85="PayPay",ROUND(K85*0.05),IF(J85="エコリング",0,ROUND(K85*0.1))))</f>
+        <f>IF(OR(K85="",J85=""),"",IF(J85="エコリング","",IF(J85="PayPay",ROUND(K85*0.05),ROUND(K85*0.1))))</f>
         <v/>
       </c>
       <c r="M85" s="8" t="n"/>
@@ -3546,7 +3546,7 @@
       <c r="J86" s="2" t="n"/>
       <c r="K86" s="4" t="n"/>
       <c r="L86" s="4">
-        <f>IF(OR(K86="",J86=""),"",IF(J86="PayPay",ROUND(K86*0.05),IF(J86="エコリング",0,ROUND(K86*0.1))))</f>
+        <f>IF(OR(K86="",J86=""),"",IF(J86="エコリング","",IF(J86="PayPay",ROUND(K86*0.05),ROUND(K86*0.1))))</f>
         <v/>
       </c>
       <c r="M86" s="4" t="n"/>
@@ -3576,7 +3576,7 @@
       <c r="J87" s="6" t="n"/>
       <c r="K87" s="8" t="n"/>
       <c r="L87" s="8">
-        <f>IF(OR(K87="",J87=""),"",IF(J87="PayPay",ROUND(K87*0.05),IF(J87="エコリング",0,ROUND(K87*0.1))))</f>
+        <f>IF(OR(K87="",J87=""),"",IF(J87="エコリング","",IF(J87="PayPay",ROUND(K87*0.05),ROUND(K87*0.1))))</f>
         <v/>
       </c>
       <c r="M87" s="8" t="n"/>
@@ -3606,7 +3606,7 @@
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="4" t="n"/>
       <c r="L88" s="4">
-        <f>IF(OR(K88="",J88=""),"",IF(J88="PayPay",ROUND(K88*0.05),IF(J88="エコリング",0,ROUND(K88*0.1))))</f>
+        <f>IF(OR(K88="",J88=""),"",IF(J88="エコリング","",IF(J88="PayPay",ROUND(K88*0.05),ROUND(K88*0.1))))</f>
         <v/>
       </c>
       <c r="M88" s="4" t="n"/>
@@ -3636,7 +3636,7 @@
       <c r="J89" s="6" t="n"/>
       <c r="K89" s="8" t="n"/>
       <c r="L89" s="8">
-        <f>IF(OR(K89="",J89=""),"",IF(J89="PayPay",ROUND(K89*0.05),IF(J89="エコリング",0,ROUND(K89*0.1))))</f>
+        <f>IF(OR(K89="",J89=""),"",IF(J89="エコリング","",IF(J89="PayPay",ROUND(K89*0.05),ROUND(K89*0.1))))</f>
         <v/>
       </c>
       <c r="M89" s="8" t="n"/>
@@ -3666,7 +3666,7 @@
       <c r="J90" s="2" t="n"/>
       <c r="K90" s="4" t="n"/>
       <c r="L90" s="4">
-        <f>IF(OR(K90="",J90=""),"",IF(J90="PayPay",ROUND(K90*0.05),IF(J90="エコリング",0,ROUND(K90*0.1))))</f>
+        <f>IF(OR(K90="",J90=""),"",IF(J90="エコリング","",IF(J90="PayPay",ROUND(K90*0.05),ROUND(K90*0.1))))</f>
         <v/>
       </c>
       <c r="M90" s="4" t="n"/>
@@ -3696,7 +3696,7 @@
       <c r="J91" s="6" t="n"/>
       <c r="K91" s="8" t="n"/>
       <c r="L91" s="8">
-        <f>IF(OR(K91="",J91=""),"",IF(J91="PayPay",ROUND(K91*0.05),IF(J91="エコリング",0,ROUND(K91*0.1))))</f>
+        <f>IF(OR(K91="",J91=""),"",IF(J91="エコリング","",IF(J91="PayPay",ROUND(K91*0.05),ROUND(K91*0.1))))</f>
         <v/>
       </c>
       <c r="M91" s="8" t="n"/>
@@ -3726,7 +3726,7 @@
       <c r="J92" s="2" t="n"/>
       <c r="K92" s="4" t="n"/>
       <c r="L92" s="4">
-        <f>IF(OR(K92="",J92=""),"",IF(J92="PayPay",ROUND(K92*0.05),IF(J92="エコリング",0,ROUND(K92*0.1))))</f>
+        <f>IF(OR(K92="",J92=""),"",IF(J92="エコリング","",IF(J92="PayPay",ROUND(K92*0.05),ROUND(K92*0.1))))</f>
         <v/>
       </c>
       <c r="M92" s="4" t="n"/>
@@ -3756,7 +3756,7 @@
       <c r="J93" s="6" t="n"/>
       <c r="K93" s="8" t="n"/>
       <c r="L93" s="8">
-        <f>IF(OR(K93="",J93=""),"",IF(J93="PayPay",ROUND(K93*0.05),IF(J93="エコリング",0,ROUND(K93*0.1))))</f>
+        <f>IF(OR(K93="",J93=""),"",IF(J93="エコリング","",IF(J93="PayPay",ROUND(K93*0.05),ROUND(K93*0.1))))</f>
         <v/>
       </c>
       <c r="M93" s="8" t="n"/>
@@ -3786,7 +3786,7 @@
       <c r="J94" s="2" t="n"/>
       <c r="K94" s="4" t="n"/>
       <c r="L94" s="4">
-        <f>IF(OR(K94="",J94=""),"",IF(J94="PayPay",ROUND(K94*0.05),IF(J94="エコリング",0,ROUND(K94*0.1))))</f>
+        <f>IF(OR(K94="",J94=""),"",IF(J94="エコリング","",IF(J94="PayPay",ROUND(K94*0.05),ROUND(K94*0.1))))</f>
         <v/>
       </c>
       <c r="M94" s="4" t="n"/>
@@ -3816,7 +3816,7 @@
       <c r="J95" s="6" t="n"/>
       <c r="K95" s="8" t="n"/>
       <c r="L95" s="8">
-        <f>IF(OR(K95="",J95=""),"",IF(J95="PayPay",ROUND(K95*0.05),IF(J95="エコリング",0,ROUND(K95*0.1))))</f>
+        <f>IF(OR(K95="",J95=""),"",IF(J95="エコリング","",IF(J95="PayPay",ROUND(K95*0.05),ROUND(K95*0.1))))</f>
         <v/>
       </c>
       <c r="M95" s="8" t="n"/>
@@ -3846,7 +3846,7 @@
       <c r="J96" s="2" t="n"/>
       <c r="K96" s="4" t="n"/>
       <c r="L96" s="4">
-        <f>IF(OR(K96="",J96=""),"",IF(J96="PayPay",ROUND(K96*0.05),IF(J96="エコリング",0,ROUND(K96*0.1))))</f>
+        <f>IF(OR(K96="",J96=""),"",IF(J96="エコリング","",IF(J96="PayPay",ROUND(K96*0.05),ROUND(K96*0.1))))</f>
         <v/>
       </c>
       <c r="M96" s="4" t="n"/>
@@ -3876,7 +3876,7 @@
       <c r="J97" s="6" t="n"/>
       <c r="K97" s="8" t="n"/>
       <c r="L97" s="8">
-        <f>IF(OR(K97="",J97=""),"",IF(J97="PayPay",ROUND(K97*0.05),IF(J97="エコリング",0,ROUND(K97*0.1))))</f>
+        <f>IF(OR(K97="",J97=""),"",IF(J97="エコリング","",IF(J97="PayPay",ROUND(K97*0.05),ROUND(K97*0.1))))</f>
         <v/>
       </c>
       <c r="M97" s="8" t="n"/>
@@ -3906,7 +3906,7 @@
       <c r="J98" s="2" t="n"/>
       <c r="K98" s="4" t="n"/>
       <c r="L98" s="4">
-        <f>IF(OR(K98="",J98=""),"",IF(J98="PayPay",ROUND(K98*0.05),IF(J98="エコリング",0,ROUND(K98*0.1))))</f>
+        <f>IF(OR(K98="",J98=""),"",IF(J98="エコリング","",IF(J98="PayPay",ROUND(K98*0.05),ROUND(K98*0.1))))</f>
         <v/>
       </c>
       <c r="M98" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       <c r="J99" s="6" t="n"/>
       <c r="K99" s="8" t="n"/>
       <c r="L99" s="8">
-        <f>IF(OR(K99="",J99=""),"",IF(J99="PayPay",ROUND(K99*0.05),IF(J99="エコリング",0,ROUND(K99*0.1))))</f>
+        <f>IF(OR(K99="",J99=""),"",IF(J99="エコリング","",IF(J99="PayPay",ROUND(K99*0.05),ROUND(K99*0.1))))</f>
         <v/>
       </c>
       <c r="M99" s="8" t="n"/>
@@ -3966,7 +3966,7 @@
       <c r="J100" s="2" t="n"/>
       <c r="K100" s="4" t="n"/>
       <c r="L100" s="4">
-        <f>IF(OR(K100="",J100=""),"",IF(J100="PayPay",ROUND(K100*0.05),IF(J100="エコリング",0,ROUND(K100*0.1))))</f>
+        <f>IF(OR(K100="",J100=""),"",IF(J100="エコリング","",IF(J100="PayPay",ROUND(K100*0.05),ROUND(K100*0.1))))</f>
         <v/>
       </c>
       <c r="M100" s="4" t="n"/>
@@ -3996,7 +3996,7 @@
       <c r="J101" s="6" t="n"/>
       <c r="K101" s="8" t="n"/>
       <c r="L101" s="8">
-        <f>IF(OR(K101="",J101=""),"",IF(J101="PayPay",ROUND(K101*0.05),IF(J101="エコリング",0,ROUND(K101*0.1))))</f>
+        <f>IF(OR(K101="",J101=""),"",IF(J101="エコリング","",IF(J101="PayPay",ROUND(K101*0.05),ROUND(K101*0.1))))</f>
         <v/>
       </c>
       <c r="M101" s="8" t="n"/>
